--- a/VerveStacks_CAN_grids_kan/vt_vervestacks_CAN_v1.xlsx
+++ b/VerveStacks_CAN_grids_kan/vt_vervestacks_CAN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46A4D661-4446-4095-9E4C-70281A1A3F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5B8F0D0-0C5C-43A0-8FC9-94BBDFE37349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3820F113-1934-43BD-9F96-1BF81D2B5985}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6D4F8A64-A361-401E-B3D4-77D04063BCB9}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -5060,7 +5060,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{037AEEAA-83C8-4410-8B00-12113DF51D20}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13BF747E-889B-4915-BCCE-9C765CC89BB2}">
   <dimension ref="B9:O14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5283,7 +5283,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{071AE52A-DBA6-494F-8847-18C4E7CA2880}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C370C97-45E9-4217-B196-7B39EA393324}">
   <dimension ref="B9:T167"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6258,19 +6258,19 @@
         <v>21</v>
       </c>
       <c r="E27">
-        <v>0.13364999999999999</v>
+        <v>8.0256000000000022E-2</v>
       </c>
       <c r="F27">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G27">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H27">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I27">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J27" t="s">
         <v>83</v>
@@ -6314,7 +6314,7 @@
         <v>86</v>
       </c>
       <c r="E28">
-        <v>8.5120000000000029E-2</v>
+        <v>6.8096000000000018E-2</v>
       </c>
       <c r="F28">
         <v>3583</v>
@@ -6370,19 +6370,19 @@
         <v>88</v>
       </c>
       <c r="E29">
-        <v>0.2482</v>
+        <v>0.18876800000000002</v>
       </c>
       <c r="F29">
-        <v>2200</v>
+        <v>2445</v>
       </c>
       <c r="G29">
-        <v>27.7</v>
+        <v>30.4</v>
       </c>
       <c r="H29">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="I29">
-        <v>0.74765000000000004</v>
+        <v>0.72770000000000001</v>
       </c>
       <c r="J29" t="s">
         <v>87</v>
@@ -6426,19 +6426,19 @@
         <v>90</v>
       </c>
       <c r="E30">
-        <v>0.27467999999999998</v>
+        <v>0.19987200000000002</v>
       </c>
       <c r="F30">
-        <v>1967</v>
+        <v>2445</v>
       </c>
       <c r="G30">
-        <v>25.2</v>
+        <v>30.4</v>
       </c>
       <c r="H30">
-        <v>2.73</v>
+        <v>3.52</v>
       </c>
       <c r="I30">
-        <v>0.76759999999999995</v>
+        <v>0.72770000000000001</v>
       </c>
       <c r="J30" t="s">
         <v>89</v>
@@ -6482,19 +6482,19 @@
         <v>86</v>
       </c>
       <c r="E31">
-        <v>0.12960000000000002</v>
+        <v>7.7824000000000018E-2</v>
       </c>
       <c r="F31">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G31">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H31">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I31">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J31" t="s">
         <v>91</v>
@@ -6538,19 +6538,19 @@
         <v>93</v>
       </c>
       <c r="E32">
-        <v>0.26705000000000001</v>
+        <v>0.19431999999999999</v>
       </c>
       <c r="F32">
-        <v>1967</v>
+        <v>2445</v>
       </c>
       <c r="G32">
-        <v>25.2</v>
+        <v>30.4</v>
       </c>
       <c r="H32">
-        <v>2.73</v>
+        <v>3.52</v>
       </c>
       <c r="I32">
-        <v>0.76759999999999995</v>
+        <v>0.72770000000000001</v>
       </c>
       <c r="J32" t="s">
         <v>92</v>
@@ -6594,19 +6594,19 @@
         <v>93</v>
       </c>
       <c r="E33">
-        <v>0.27467999999999998</v>
+        <v>0.19987200000000002</v>
       </c>
       <c r="F33">
-        <v>1967</v>
+        <v>2445</v>
       </c>
       <c r="G33">
-        <v>25.2</v>
+        <v>30.4</v>
       </c>
       <c r="H33">
-        <v>2.73</v>
+        <v>3.52</v>
       </c>
       <c r="I33">
-        <v>0.76759999999999995</v>
+        <v>0.72770000000000001</v>
       </c>
       <c r="J33" t="s">
         <v>94</v>
@@ -6650,19 +6650,19 @@
         <v>67</v>
       </c>
       <c r="E34">
-        <v>0.12960000000000002</v>
+        <v>7.7824000000000018E-2</v>
       </c>
       <c r="F34">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G34">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H34">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I34">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J34" t="s">
         <v>95</v>
@@ -6706,19 +6706,19 @@
         <v>21</v>
       </c>
       <c r="E35">
-        <v>0.12960000000000002</v>
+        <v>7.7824000000000018E-2</v>
       </c>
       <c r="F35">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G35">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H35">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I35">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J35" t="s">
         <v>96</v>
@@ -6762,19 +6762,19 @@
         <v>21</v>
       </c>
       <c r="E36">
-        <v>0.12960000000000002</v>
+        <v>7.7824000000000018E-2</v>
       </c>
       <c r="F36">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G36">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H36">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I36">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J36" t="s">
         <v>97</v>
@@ -6818,19 +6818,19 @@
         <v>21</v>
       </c>
       <c r="E37">
-        <v>0.13364999999999999</v>
+        <v>8.0256000000000022E-2</v>
       </c>
       <c r="F37">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G37">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H37">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I37">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J37" t="s">
         <v>98</v>
@@ -6874,19 +6874,19 @@
         <v>21</v>
       </c>
       <c r="E38">
-        <v>0.13364999999999999</v>
+        <v>8.0256000000000022E-2</v>
       </c>
       <c r="F38">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G38">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H38">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I38">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J38" t="s">
         <v>99</v>
@@ -6930,7 +6930,7 @@
         <v>101</v>
       </c>
       <c r="E39">
-        <v>9.1200000000000003E-2</v>
+        <v>7.2960000000000011E-2</v>
       </c>
       <c r="F39">
         <v>3583</v>
@@ -6986,19 +6986,19 @@
         <v>101</v>
       </c>
       <c r="E40">
-        <v>0.13770000000000002</v>
+        <v>8.2688000000000025E-2</v>
       </c>
       <c r="F40">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G40">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H40">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I40">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J40" t="s">
         <v>102</v>
@@ -7042,19 +7042,19 @@
         <v>21</v>
       </c>
       <c r="E41">
-        <v>0.12960000000000002</v>
+        <v>7.7824000000000018E-2</v>
       </c>
       <c r="F41">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G41">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H41">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I41">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J41" t="s">
         <v>103</v>
@@ -7098,19 +7098,19 @@
         <v>105</v>
       </c>
       <c r="E42">
-        <v>0.13770000000000002</v>
+        <v>8.2688000000000025E-2</v>
       </c>
       <c r="F42">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G42">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H42">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I42">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J42" t="s">
         <v>104</v>
@@ -7154,19 +7154,19 @@
         <v>105</v>
       </c>
       <c r="E43">
-        <v>0.1729</v>
+        <v>8.5120000000000001E-2</v>
       </c>
       <c r="F43">
-        <v>2757</v>
+        <v>3583</v>
       </c>
       <c r="G43">
-        <v>39.200000000000003</v>
+        <v>49</v>
       </c>
       <c r="H43">
-        <v>3.35</v>
+        <v>4.59</v>
       </c>
       <c r="I43">
-        <v>0.63080000000000003</v>
+        <v>0.5605</v>
       </c>
       <c r="J43" t="s">
         <v>106</v>
@@ -7210,19 +7210,19 @@
         <v>86</v>
       </c>
       <c r="E44">
-        <v>0.13770000000000002</v>
+        <v>8.2688000000000025E-2</v>
       </c>
       <c r="F44">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G44">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H44">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I44">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J44" t="s">
         <v>107</v>
@@ -7266,19 +7266,19 @@
         <v>93</v>
       </c>
       <c r="E45">
-        <v>0.30138500000000001</v>
+        <v>0.23068000000000005</v>
       </c>
       <c r="F45">
-        <v>1967</v>
+        <v>2200</v>
       </c>
       <c r="G45">
-        <v>25.2</v>
+        <v>27.7</v>
       </c>
       <c r="H45">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="I45">
-        <v>0.76759999999999995</v>
+        <v>0.74765000000000004</v>
       </c>
       <c r="J45" t="s">
         <v>108</v>
@@ -7322,7 +7322,7 @@
         <v>111</v>
       </c>
       <c r="E46">
-        <v>0.4375</v>
+        <v>0.35</v>
       </c>
       <c r="F46">
         <v>1365</v>
@@ -7378,7 +7378,7 @@
         <v>113</v>
       </c>
       <c r="E47">
-        <v>0.50749999999999995</v>
+        <v>0.40599999999999992</v>
       </c>
       <c r="F47">
         <v>1365</v>
@@ -7434,7 +7434,7 @@
         <v>115</v>
       </c>
       <c r="E48">
-        <v>0.52500000000000002</v>
+        <v>0.42</v>
       </c>
       <c r="F48">
         <v>1365</v>
@@ -7490,7 +7490,7 @@
         <v>115</v>
       </c>
       <c r="E49">
-        <v>0.52500000000000002</v>
+        <v>0.42</v>
       </c>
       <c r="F49">
         <v>1365</v>
@@ -7546,7 +7546,7 @@
         <v>105</v>
       </c>
       <c r="E50">
-        <v>0.50749999999999995</v>
+        <v>0.40600000000000003</v>
       </c>
       <c r="F50">
         <v>1365</v>
@@ -7602,7 +7602,7 @@
         <v>105</v>
       </c>
       <c r="E51">
-        <v>0.52500000000000002</v>
+        <v>0.41999999999999993</v>
       </c>
       <c r="F51">
         <v>1365</v>
@@ -7658,7 +7658,7 @@
         <v>120</v>
       </c>
       <c r="E52">
-        <v>0.45500000000000002</v>
+        <v>0.36400000000000005</v>
       </c>
       <c r="F52">
         <v>1365</v>
@@ -7714,7 +7714,7 @@
         <v>122</v>
       </c>
       <c r="E53">
-        <v>0.45500000000000002</v>
+        <v>0.36400000000000005</v>
       </c>
       <c r="F53">
         <v>1365</v>
@@ -7770,7 +7770,7 @@
         <v>67</v>
       </c>
       <c r="E54">
-        <v>0.45500000000000002</v>
+        <v>0.36400000000000005</v>
       </c>
       <c r="F54">
         <v>1365</v>
@@ -7826,7 +7826,7 @@
         <v>125</v>
       </c>
       <c r="E55">
-        <v>0.47687499999999999</v>
+        <v>0.38150000000000006</v>
       </c>
       <c r="F55">
         <v>1365</v>
@@ -7882,7 +7882,7 @@
         <v>111</v>
       </c>
       <c r="E56">
-        <v>0.47687499999999999</v>
+        <v>0.38150000000000006</v>
       </c>
       <c r="F56">
         <v>1365</v>
@@ -7938,7 +7938,7 @@
         <v>120</v>
       </c>
       <c r="E57">
-        <v>0.47687499999999999</v>
+        <v>0.38150000000000006</v>
       </c>
       <c r="F57">
         <v>1365</v>
@@ -7994,7 +7994,7 @@
         <v>129</v>
       </c>
       <c r="E58">
-        <v>0.4375</v>
+        <v>0.35</v>
       </c>
       <c r="F58">
         <v>1365</v>
@@ -8050,7 +8050,7 @@
         <v>131</v>
       </c>
       <c r="E59">
-        <v>0.45500000000000002</v>
+        <v>0.36400000000000005</v>
       </c>
       <c r="F59">
         <v>1365</v>
@@ -8106,7 +8106,7 @@
         <v>133</v>
       </c>
       <c r="E60">
-        <v>0.45500000000000002</v>
+        <v>0.36400000000000005</v>
       </c>
       <c r="F60">
         <v>1365</v>
@@ -8162,7 +8162,7 @@
         <v>135</v>
       </c>
       <c r="E61">
-        <v>0.4375</v>
+        <v>0.35</v>
       </c>
       <c r="F61">
         <v>1365</v>
@@ -8218,7 +8218,7 @@
         <v>93</v>
       </c>
       <c r="E62">
-        <v>0.52500000000000002</v>
+        <v>0.42</v>
       </c>
       <c r="F62">
         <v>1365</v>
@@ -8274,7 +8274,7 @@
         <v>93</v>
       </c>
       <c r="E63">
-        <v>0.52500000000000002</v>
+        <v>0.42</v>
       </c>
       <c r="F63">
         <v>1365</v>
@@ -8330,7 +8330,7 @@
         <v>139</v>
       </c>
       <c r="E64">
-        <v>0.47687499999999999</v>
+        <v>0.38150000000000006</v>
       </c>
       <c r="F64">
         <v>1365</v>
@@ -8386,7 +8386,7 @@
         <v>141</v>
       </c>
       <c r="E65">
-        <v>0.49000000000000005</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="F65">
         <v>1365</v>
@@ -8442,7 +8442,7 @@
         <v>111</v>
       </c>
       <c r="E66">
-        <v>0.47687499999999999</v>
+        <v>0.38150000000000006</v>
       </c>
       <c r="F66">
         <v>1365</v>
@@ -8498,7 +8498,7 @@
         <v>144</v>
       </c>
       <c r="E67">
-        <v>0.4375</v>
+        <v>0.35</v>
       </c>
       <c r="F67">
         <v>1365</v>
@@ -8554,7 +8554,7 @@
         <v>146</v>
       </c>
       <c r="E68">
-        <v>0.45500000000000002</v>
+        <v>0.36400000000000005</v>
       </c>
       <c r="F68">
         <v>1365</v>
@@ -8610,7 +8610,7 @@
         <v>113</v>
       </c>
       <c r="E69">
-        <v>0.4375</v>
+        <v>0.35</v>
       </c>
       <c r="F69">
         <v>1365</v>
@@ -8666,7 +8666,7 @@
         <v>144</v>
       </c>
       <c r="E70">
-        <v>0.4375</v>
+        <v>0.35</v>
       </c>
       <c r="F70">
         <v>1365</v>
@@ -8722,7 +8722,7 @@
         <v>150</v>
       </c>
       <c r="E71">
-        <v>0.47687499999999999</v>
+        <v>0.38150000000000006</v>
       </c>
       <c r="F71">
         <v>1365</v>
@@ -8778,7 +8778,7 @@
         <v>152</v>
       </c>
       <c r="E72">
-        <v>0.45500000000000002</v>
+        <v>0.36400000000000005</v>
       </c>
       <c r="F72">
         <v>1365</v>
@@ -8834,7 +8834,7 @@
         <v>152</v>
       </c>
       <c r="E73">
-        <v>0.45500000000000002</v>
+        <v>0.36400000000000005</v>
       </c>
       <c r="F73">
         <v>1365</v>
@@ -8890,7 +8890,7 @@
         <v>155</v>
       </c>
       <c r="E74">
-        <v>0.45500000000000002</v>
+        <v>0.36400000000000005</v>
       </c>
       <c r="F74">
         <v>1365</v>
@@ -8946,7 +8946,7 @@
         <v>133</v>
       </c>
       <c r="E75">
-        <v>0.4375</v>
+        <v>0.35</v>
       </c>
       <c r="F75">
         <v>1365</v>
@@ -9002,7 +9002,7 @@
         <v>158</v>
       </c>
       <c r="E76">
-        <v>0.47687499999999999</v>
+        <v>0.38150000000000001</v>
       </c>
       <c r="F76">
         <v>1365</v>
@@ -9058,7 +9058,7 @@
         <v>160</v>
       </c>
       <c r="E77">
-        <v>0.47687499999999999</v>
+        <v>0.38150000000000006</v>
       </c>
       <c r="F77">
         <v>1365</v>
@@ -9114,7 +9114,7 @@
         <v>133</v>
       </c>
       <c r="E78">
-        <v>0.49000000000000005</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="F78">
         <v>1365</v>
@@ -9170,7 +9170,7 @@
         <v>163</v>
       </c>
       <c r="E79">
-        <v>0.45500000000000002</v>
+        <v>0.36400000000000005</v>
       </c>
       <c r="F79">
         <v>1365</v>
@@ -9226,7 +9226,7 @@
         <v>133</v>
       </c>
       <c r="E80">
-        <v>0.29750000000000004</v>
+        <v>0.23800000000000002</v>
       </c>
       <c r="F80">
         <v>1365</v>
@@ -9282,7 +9282,7 @@
         <v>141</v>
       </c>
       <c r="E81">
-        <v>0.47687499999999999</v>
+        <v>0.38150000000000006</v>
       </c>
       <c r="F81">
         <v>1365</v>
@@ -9338,7 +9338,7 @@
         <v>167</v>
       </c>
       <c r="E82">
-        <v>0.50749999999999995</v>
+        <v>0.40599999999999992</v>
       </c>
       <c r="F82">
         <v>1365</v>
@@ -9394,7 +9394,7 @@
         <v>141</v>
       </c>
       <c r="E83">
-        <v>0.45500000000000002</v>
+        <v>0.36400000000000005</v>
       </c>
       <c r="F83">
         <v>1365</v>
@@ -9450,7 +9450,7 @@
         <v>141</v>
       </c>
       <c r="E84">
-        <v>0.45500000000000002</v>
+        <v>0.36400000000000005</v>
       </c>
       <c r="F84">
         <v>1365</v>
@@ -9506,7 +9506,7 @@
         <v>163</v>
       </c>
       <c r="E85">
-        <v>0.52500000000000002</v>
+        <v>0.42</v>
       </c>
       <c r="F85">
         <v>1365</v>
@@ -9562,7 +9562,7 @@
         <v>163</v>
       </c>
       <c r="E86">
-        <v>0.52500000000000002</v>
+        <v>0.42</v>
       </c>
       <c r="F86">
         <v>1365</v>
@@ -9618,7 +9618,7 @@
         <v>173</v>
       </c>
       <c r="E87">
-        <v>0.45500000000000002</v>
+        <v>0.36400000000000005</v>
       </c>
       <c r="F87">
         <v>1365</v>
@@ -9674,7 +9674,7 @@
         <v>139</v>
       </c>
       <c r="E88">
-        <v>0.45500000000000002</v>
+        <v>0.36400000000000005</v>
       </c>
       <c r="F88">
         <v>1365</v>
@@ -9730,7 +9730,7 @@
         <v>111</v>
       </c>
       <c r="E89">
-        <v>0.4375</v>
+        <v>0.35</v>
       </c>
       <c r="F89">
         <v>1365</v>
@@ -9786,7 +9786,7 @@
         <v>35</v>
       </c>
       <c r="E90">
-        <v>0.4375</v>
+        <v>0.35</v>
       </c>
       <c r="F90">
         <v>1365</v>
@@ -9842,7 +9842,7 @@
         <v>178</v>
       </c>
       <c r="E91">
-        <v>0.45500000000000002</v>
+        <v>0.36399999999999999</v>
       </c>
       <c r="F91">
         <v>1365</v>
@@ -9898,7 +9898,7 @@
         <v>180</v>
       </c>
       <c r="E92">
-        <v>0.49000000000000005</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="F92">
         <v>1365</v>
@@ -9954,7 +9954,7 @@
         <v>67</v>
       </c>
       <c r="E93">
-        <v>0.50749999999999995</v>
+        <v>0.40599999999999992</v>
       </c>
       <c r="F93">
         <v>1365</v>
@@ -10010,7 +10010,7 @@
         <v>133</v>
       </c>
       <c r="E94">
-        <v>0.49000000000000005</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="F94">
         <v>1365</v>
@@ -10066,7 +10066,7 @@
         <v>133</v>
       </c>
       <c r="E95">
-        <v>0.29750000000000004</v>
+        <v>0.23800000000000002</v>
       </c>
       <c r="F95">
         <v>1365</v>
@@ -10122,7 +10122,7 @@
         <v>185</v>
       </c>
       <c r="E96">
-        <v>0.49000000000000005</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="F96">
         <v>1365</v>
@@ -10178,7 +10178,7 @@
         <v>187</v>
       </c>
       <c r="E97">
-        <v>0.4375</v>
+        <v>0.35</v>
       </c>
       <c r="F97">
         <v>1365</v>
@@ -10234,7 +10234,7 @@
         <v>189</v>
       </c>
       <c r="E98">
-        <v>0.49000000000000005</v>
+        <v>0.39200000000000013</v>
       </c>
       <c r="F98">
         <v>1365</v>
@@ -10290,7 +10290,7 @@
         <v>155</v>
       </c>
       <c r="E99">
-        <v>0.231875</v>
+        <v>0.1855</v>
       </c>
       <c r="F99">
         <v>1365</v>
@@ -10346,7 +10346,7 @@
         <v>125</v>
       </c>
       <c r="E100">
-        <v>0.231875</v>
+        <v>0.1855</v>
       </c>
       <c r="F100">
         <v>1365</v>
@@ -10402,7 +10402,7 @@
         <v>125</v>
       </c>
       <c r="E101">
-        <v>0.231875</v>
+        <v>0.1855</v>
       </c>
       <c r="F101">
         <v>1365</v>
@@ -10458,7 +10458,7 @@
         <v>125</v>
       </c>
       <c r="E102">
-        <v>0.231875</v>
+        <v>0.1855</v>
       </c>
       <c r="F102">
         <v>1365</v>
@@ -10514,7 +10514,7 @@
         <v>125</v>
       </c>
       <c r="E103">
-        <v>0.231875</v>
+        <v>0.1855</v>
       </c>
       <c r="F103">
         <v>1365</v>
@@ -10570,7 +10570,7 @@
         <v>86</v>
       </c>
       <c r="E104">
-        <v>0.25374999999999998</v>
+        <v>0.20299999999999996</v>
       </c>
       <c r="F104">
         <v>1365</v>
@@ -10626,7 +10626,7 @@
         <v>86</v>
       </c>
       <c r="E105">
-        <v>0.25374999999999998</v>
+        <v>0.20299999999999996</v>
       </c>
       <c r="F105">
         <v>1365</v>
@@ -10682,7 +10682,7 @@
         <v>198</v>
       </c>
       <c r="E106">
-        <v>0.25374999999999998</v>
+        <v>0.20299999999999996</v>
       </c>
       <c r="F106">
         <v>1365</v>
@@ -10738,7 +10738,7 @@
         <v>198</v>
       </c>
       <c r="E107">
-        <v>0.25374999999999998</v>
+        <v>0.20299999999999996</v>
       </c>
       <c r="F107">
         <v>1365</v>
@@ -10794,7 +10794,7 @@
         <v>67</v>
       </c>
       <c r="E108">
-        <v>0.27124999999999999</v>
+        <v>0.217</v>
       </c>
       <c r="F108">
         <v>1365</v>
@@ -10850,7 +10850,7 @@
         <v>202</v>
       </c>
       <c r="E109">
-        <v>0.25374999999999998</v>
+        <v>0.20299999999999996</v>
       </c>
       <c r="F109">
         <v>1365</v>
@@ -10906,7 +10906,7 @@
         <v>67</v>
       </c>
       <c r="E110">
-        <v>0.27124999999999999</v>
+        <v>0.217</v>
       </c>
       <c r="F110">
         <v>1365</v>
@@ -10962,7 +10962,7 @@
         <v>205</v>
       </c>
       <c r="E111">
-        <v>0.25374999999999998</v>
+        <v>0.20299999999999996</v>
       </c>
       <c r="F111">
         <v>1365</v>
@@ -11018,7 +11018,7 @@
         <v>207</v>
       </c>
       <c r="E112">
-        <v>0.231875</v>
+        <v>0.1855</v>
       </c>
       <c r="F112">
         <v>1365</v>
@@ -11074,7 +11074,7 @@
         <v>207</v>
       </c>
       <c r="E113">
-        <v>0.27124999999999999</v>
+        <v>0.21699999999999997</v>
       </c>
       <c r="F113">
         <v>1365</v>
@@ -11130,7 +11130,7 @@
         <v>141</v>
       </c>
       <c r="E114">
-        <v>0.25374999999999998</v>
+        <v>0.20299999999999996</v>
       </c>
       <c r="F114">
         <v>1365</v>
@@ -11186,7 +11186,7 @@
         <v>61</v>
       </c>
       <c r="E115">
-        <v>0.231875</v>
+        <v>0.1855</v>
       </c>
       <c r="F115">
         <v>1365</v>
@@ -11242,7 +11242,7 @@
         <v>160</v>
       </c>
       <c r="E116">
-        <v>0.27124999999999999</v>
+        <v>0.217</v>
       </c>
       <c r="F116">
         <v>1365</v>
@@ -11298,7 +11298,7 @@
         <v>160</v>
       </c>
       <c r="E117">
-        <v>0.27124999999999999</v>
+        <v>0.217</v>
       </c>
       <c r="F117">
         <v>1365</v>
@@ -11354,7 +11354,7 @@
         <v>61</v>
       </c>
       <c r="E118">
-        <v>0.231875</v>
+        <v>0.1855</v>
       </c>
       <c r="F118">
         <v>1365</v>
@@ -11410,7 +11410,7 @@
         <v>61</v>
       </c>
       <c r="E119">
-        <v>0.231875</v>
+        <v>0.1855</v>
       </c>
       <c r="F119">
         <v>1365</v>
@@ -11466,7 +11466,7 @@
         <v>216</v>
       </c>
       <c r="E120">
-        <v>0.27124999999999999</v>
+        <v>0.217</v>
       </c>
       <c r="F120">
         <v>1365</v>
@@ -11522,7 +11522,7 @@
         <v>189</v>
       </c>
       <c r="E121">
-        <v>0.27124999999999999</v>
+        <v>0.217</v>
       </c>
       <c r="F121">
         <v>1365</v>
@@ -11578,7 +11578,7 @@
         <v>216</v>
       </c>
       <c r="E122">
-        <v>0.27124999999999999</v>
+        <v>0.21700000000000003</v>
       </c>
       <c r="F122">
         <v>1365</v>
@@ -11634,7 +11634,7 @@
         <v>220</v>
       </c>
       <c r="E123">
-        <v>0.25374999999999998</v>
+        <v>0.20299999999999996</v>
       </c>
       <c r="F123">
         <v>1365</v>
@@ -11690,7 +11690,7 @@
         <v>222</v>
       </c>
       <c r="E124">
-        <v>0.22312499999999999</v>
+        <v>0.17850000000000002</v>
       </c>
       <c r="F124">
         <v>1365</v>
@@ -11746,7 +11746,7 @@
         <v>224</v>
       </c>
       <c r="E125">
-        <v>0.28000000000000003</v>
+        <v>0.22400000000000003</v>
       </c>
       <c r="F125">
         <v>1365</v>
@@ -11802,7 +11802,7 @@
         <v>226</v>
       </c>
       <c r="E126">
-        <v>0.25374999999999998</v>
+        <v>0.20299999999999996</v>
       </c>
       <c r="F126">
         <v>1365</v>
@@ -11858,7 +11858,7 @@
         <v>67</v>
       </c>
       <c r="E127">
-        <v>0.24500000000000002</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="F127">
         <v>1365</v>
@@ -11914,7 +11914,7 @@
         <v>207</v>
       </c>
       <c r="E128">
-        <v>0.25374999999999998</v>
+        <v>0.20299999999999996</v>
       </c>
       <c r="F128">
         <v>1365</v>
@@ -11970,7 +11970,7 @@
         <v>133</v>
       </c>
       <c r="E129">
-        <v>0.231875</v>
+        <v>0.1855</v>
       </c>
       <c r="F129">
         <v>1365</v>
@@ -12026,7 +12026,7 @@
         <v>231</v>
       </c>
       <c r="E130">
-        <v>0.25374999999999998</v>
+        <v>0.20299999999999996</v>
       </c>
       <c r="F130">
         <v>1365</v>
@@ -12082,7 +12082,7 @@
         <v>189</v>
       </c>
       <c r="E131">
-        <v>0.231875</v>
+        <v>0.1855</v>
       </c>
       <c r="F131">
         <v>1365</v>
@@ -12138,7 +12138,7 @@
         <v>67</v>
       </c>
       <c r="E132">
-        <v>0.27124999999999999</v>
+        <v>0.21700000000000003</v>
       </c>
       <c r="F132">
         <v>1365</v>
@@ -12194,7 +12194,7 @@
         <v>113</v>
       </c>
       <c r="E133">
-        <v>0.28875000000000001</v>
+        <v>0.23100000000000001</v>
       </c>
       <c r="F133">
         <v>1365</v>
@@ -12250,7 +12250,7 @@
         <v>113</v>
       </c>
       <c r="E134">
-        <v>0.28875000000000001</v>
+        <v>0.23100000000000001</v>
       </c>
       <c r="F134">
         <v>1365</v>
@@ -12306,7 +12306,7 @@
         <v>113</v>
       </c>
       <c r="E135">
-        <v>0.28875000000000001</v>
+        <v>0.23100000000000001</v>
       </c>
       <c r="F135">
         <v>1365</v>
@@ -12362,7 +12362,7 @@
         <v>113</v>
       </c>
       <c r="E136">
-        <v>0.28875000000000001</v>
+        <v>0.23100000000000001</v>
       </c>
       <c r="F136">
         <v>1365</v>
@@ -12418,7 +12418,7 @@
         <v>111</v>
       </c>
       <c r="E137">
-        <v>0.29750000000000004</v>
+        <v>0.23800000000000002</v>
       </c>
       <c r="F137">
         <v>1365</v>
@@ -12474,7 +12474,7 @@
         <v>133</v>
       </c>
       <c r="E138">
-        <v>0.25374999999999998</v>
+        <v>0.20299999999999996</v>
       </c>
       <c r="F138">
         <v>1365</v>
@@ -12530,7 +12530,7 @@
         <v>88</v>
       </c>
       <c r="E139">
-        <v>0.31937500000000002</v>
+        <v>0.25549999999999995</v>
       </c>
       <c r="F139">
         <v>1365</v>
@@ -12586,7 +12586,7 @@
         <v>93</v>
       </c>
       <c r="E140">
-        <v>0.31937500000000002</v>
+        <v>0.25549999999999995</v>
       </c>
       <c r="F140">
         <v>1365</v>
@@ -12642,7 +12642,7 @@
         <v>243</v>
       </c>
       <c r="E141">
-        <v>0.31937500000000002</v>
+        <v>0.25549999999999995</v>
       </c>
       <c r="F141">
         <v>1365</v>
@@ -12698,7 +12698,7 @@
         <v>245</v>
       </c>
       <c r="E142">
-        <v>0.31937500000000002</v>
+        <v>0.25549999999999995</v>
       </c>
       <c r="F142">
         <v>1365</v>
@@ -12754,7 +12754,7 @@
         <v>247</v>
       </c>
       <c r="E143">
-        <v>0.31937500000000002</v>
+        <v>0.25549999999999995</v>
       </c>
       <c r="F143">
         <v>1365</v>
@@ -12810,7 +12810,7 @@
         <v>247</v>
       </c>
       <c r="E144">
-        <v>0.31937500000000002</v>
+        <v>0.25549999999999995</v>
       </c>
       <c r="F144">
         <v>1365</v>
@@ -12866,7 +12866,7 @@
         <v>245</v>
       </c>
       <c r="E145">
-        <v>0.31937500000000002</v>
+        <v>0.25549999999999995</v>
       </c>
       <c r="F145">
         <v>1365</v>
@@ -12922,7 +12922,7 @@
         <v>243</v>
       </c>
       <c r="E146">
-        <v>0.30187499999999995</v>
+        <v>0.24149999999999999</v>
       </c>
       <c r="F146">
         <v>1365</v>
@@ -12978,7 +12978,7 @@
         <v>88</v>
       </c>
       <c r="E147">
-        <v>0.30187499999999995</v>
+        <v>0.24149999999999999</v>
       </c>
       <c r="F147">
         <v>1365</v>
@@ -13034,7 +13034,7 @@
         <v>216</v>
       </c>
       <c r="E148">
-        <v>0.29582661290322582</v>
+        <v>0.23666129032258065</v>
       </c>
       <c r="F148">
         <v>1365</v>
@@ -13090,7 +13090,7 @@
         <v>61</v>
       </c>
       <c r="E149">
-        <v>0.29312500000000002</v>
+        <v>0.23450000000000004</v>
       </c>
       <c r="F149">
         <v>1365</v>
@@ -13146,7 +13146,7 @@
         <v>255</v>
       </c>
       <c r="E150">
-        <v>0.30187499999999995</v>
+        <v>0.24149999999999999</v>
       </c>
       <c r="F150">
         <v>1365</v>
@@ -13426,7 +13426,7 @@
         <v>582</v>
       </c>
       <c r="E155">
-        <v>0.22312499999999999</v>
+        <v>0.17850000000000002</v>
       </c>
       <c r="F155">
         <v>1365</v>
@@ -13482,7 +13482,7 @@
         <v>582</v>
       </c>
       <c r="E156">
-        <v>0.22312499999999999</v>
+        <v>0.17850000000000002</v>
       </c>
       <c r="F156">
         <v>1365</v>
@@ -13538,7 +13538,7 @@
         <v>582</v>
       </c>
       <c r="E157">
-        <v>0.22312499999999999</v>
+        <v>0.17850000000000002</v>
       </c>
       <c r="F157">
         <v>1365</v>
@@ -13594,7 +13594,7 @@
         <v>582</v>
       </c>
       <c r="E158">
-        <v>0.22312499999999999</v>
+        <v>0.17850000000000002</v>
       </c>
       <c r="F158">
         <v>1365</v>
@@ -13650,7 +13650,7 @@
         <v>582</v>
       </c>
       <c r="E159">
-        <v>0.22312499999999999</v>
+        <v>0.17850000000000002</v>
       </c>
       <c r="F159">
         <v>1365</v>
@@ -13706,7 +13706,7 @@
         <v>101</v>
       </c>
       <c r="E160">
-        <v>0.23624999999999999</v>
+        <v>0.18900000000000003</v>
       </c>
       <c r="F160">
         <v>1365</v>
@@ -13762,7 +13762,7 @@
         <v>21</v>
       </c>
       <c r="E161">
-        <v>0.28437499999999999</v>
+        <v>0.22750000000000001</v>
       </c>
       <c r="F161">
         <v>1365</v>
@@ -13818,7 +13818,7 @@
         <v>21</v>
       </c>
       <c r="E162">
-        <v>0.25374999999999998</v>
+        <v>0.20299999999999996</v>
       </c>
       <c r="F162">
         <v>1365</v>
@@ -13874,7 +13874,7 @@
         <v>21</v>
       </c>
       <c r="E163">
-        <v>0.25374999999999998</v>
+        <v>0.20299999999999996</v>
       </c>
       <c r="F163">
         <v>1365</v>
@@ -13930,7 +13930,7 @@
         <v>21</v>
       </c>
       <c r="E164">
-        <v>0.25374999999999998</v>
+        <v>0.20299999999999996</v>
       </c>
       <c r="F164">
         <v>1365</v>
@@ -13986,7 +13986,7 @@
         <v>593</v>
       </c>
       <c r="E165">
-        <v>0.28000000000000003</v>
+        <v>0.22400000000000003</v>
       </c>
       <c r="F165">
         <v>1365</v>
@@ -14042,7 +14042,7 @@
         <v>593</v>
       </c>
       <c r="E166">
-        <v>0.28000000000000003</v>
+        <v>0.22400000000000003</v>
       </c>
       <c r="F166">
         <v>1365</v>
@@ -14098,7 +14098,7 @@
         <v>593</v>
       </c>
       <c r="E167">
-        <v>0.28000000000000003</v>
+        <v>0.22400000000000003</v>
       </c>
       <c r="F167">
         <v>1365</v>
@@ -14149,7 +14149,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{022632A9-942C-4679-A120-644D46AFCEF0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5375050F-B8DA-45AF-8497-C9A2E4D3B8BD}">
   <dimension ref="B9:T149"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21386,7 +21386,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB7429BD-DCB7-4055-9A39-CDCFE2AA372F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3D1A311-68C5-433C-A77F-3F5BF9F13361}">
   <dimension ref="B9:T679"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21471,7 +21471,7 @@
         <v>0.18923300970873791</v>
       </c>
       <c r="G11">
-        <v>0.33</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="H11">
         <v>4024.9999999999995</v>
@@ -21524,7 +21524,7 @@
         <v>8.2000000000000003E-2</v>
       </c>
       <c r="G12">
-        <v>0.255</v>
+        <v>0.20400000000000001</v>
       </c>
       <c r="H12">
         <v>4725</v>
@@ -21577,7 +21577,7 @@
         <v>0.10064077669902916</v>
       </c>
       <c r="G13">
-        <v>0.33</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="H13">
         <v>4024.9999999999991</v>
@@ -21630,7 +21630,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
       <c r="G14">
-        <v>0.31</v>
+        <v>0.248</v>
       </c>
       <c r="H14">
         <v>4024.9999999999991</v>
@@ -21683,7 +21683,7 @@
         <v>0.06</v>
       </c>
       <c r="G15">
-        <v>0.31</v>
+        <v>0.24799999999999997</v>
       </c>
       <c r="H15">
         <v>4024.9999999999995</v>
@@ -21736,7 +21736,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="G16">
-        <v>0.26500000000000001</v>
+        <v>0.21200000000000002</v>
       </c>
       <c r="H16">
         <v>4024.9999999999991</v>
@@ -21789,7 +21789,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="G17">
-        <v>0.26500000000000001</v>
+        <v>0.21200000000000002</v>
       </c>
       <c r="H17">
         <v>4024.9999999999995</v>
@@ -21842,7 +21842,7 @@
         <v>6.3E-2</v>
       </c>
       <c r="G18">
-        <v>0.31</v>
+        <v>0.248</v>
       </c>
       <c r="H18">
         <v>4024.9999999999995</v>
@@ -21895,7 +21895,7 @@
         <v>0.05</v>
       </c>
       <c r="G19">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="H19">
         <v>4725</v>
@@ -21948,7 +21948,7 @@
         <v>6.3E-2</v>
       </c>
       <c r="G20">
-        <v>0.31</v>
+        <v>0.248</v>
       </c>
       <c r="H20">
         <v>4024.9999999999995</v>
@@ -22001,7 +22001,7 @@
         <v>0.06</v>
       </c>
       <c r="G21">
-        <v>0.31</v>
+        <v>0.24799999999999997</v>
       </c>
       <c r="H21">
         <v>4024.9999999999995</v>
@@ -22054,7 +22054,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="G22">
-        <v>0.31</v>
+        <v>0.248</v>
       </c>
       <c r="H22">
         <v>4024.9999999999995</v>
@@ -22107,7 +22107,7 @@
         <v>0.05</v>
       </c>
       <c r="G23">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="H23">
         <v>4725</v>
@@ -22160,7 +22160,7 @@
         <v>6.2E-2</v>
       </c>
       <c r="G24">
-        <v>0.31</v>
+        <v>0.248</v>
       </c>
       <c r="H24">
         <v>4024.9999999999995</v>
@@ -22213,7 +22213,7 @@
         <v>0.20499999999999999</v>
       </c>
       <c r="G25">
-        <v>0.255</v>
+        <v>0.20400000000000001</v>
       </c>
       <c r="H25">
         <v>4024.9999999999995</v>
@@ -22266,7 +22266,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="G26">
-        <v>0.28000000000000003</v>
+        <v>0.22400000000000003</v>
       </c>
       <c r="H26">
         <v>4725</v>
@@ -22319,7 +22319,7 @@
         <v>2.2679611650485442E-2</v>
       </c>
       <c r="G27">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H27">
         <v>4725</v>
@@ -22372,7 +22372,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="G28">
-        <v>0.24</v>
+        <v>0.192</v>
       </c>
       <c r="H28">
         <v>4725</v>
@@ -22425,7 +22425,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="G29">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="H29">
         <v>4725</v>
@@ -22478,7 +22478,7 @@
         <v>9.0718446601941768E-2</v>
       </c>
       <c r="G30">
-        <v>0.33</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="H30">
         <v>4024.9999999999995</v>
@@ -22531,7 +22531,7 @@
         <v>0.04</v>
       </c>
       <c r="G31">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="H31">
         <v>4725</v>
@@ -22584,7 +22584,7 @@
         <v>8.2213592233009725E-2</v>
       </c>
       <c r="G32">
-        <v>0.33</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="H32">
         <v>4024.9999999999995</v>
@@ -22637,7 +22637,7 @@
         <v>3.6145631067961176E-2</v>
       </c>
       <c r="G33">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H33">
         <v>4725</v>
@@ -22690,7 +22690,7 @@
         <v>6.2E-2</v>
       </c>
       <c r="G34">
-        <v>0.30000000000000004</v>
+        <v>0.24</v>
       </c>
       <c r="H34">
         <v>4725</v>
@@ -22743,7 +22743,7 @@
         <v>0.12402912621359226</v>
       </c>
       <c r="G35">
-        <v>0.33</v>
+        <v>0.26399999999999996</v>
       </c>
       <c r="H35">
         <v>4024.9999999999995</v>
@@ -22796,7 +22796,7 @@
         <v>4.677669902912622E-2</v>
       </c>
       <c r="G36">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H36">
         <v>4725</v>
@@ -22849,7 +22849,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G37">
-        <v>0.3</v>
+        <v>0.24000000000000002</v>
       </c>
       <c r="H37">
         <v>4725</v>
@@ -22902,7 +22902,7 @@
         <v>3.0475728155339811E-2</v>
       </c>
       <c r="G38">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H38">
         <v>4725</v>
@@ -22955,7 +22955,7 @@
         <v>3.5436893203883497E-2</v>
       </c>
       <c r="G39">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H39">
         <v>4725</v>
@@ -23008,7 +23008,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="G40">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="H40">
         <v>4725</v>
@@ -23061,7 +23061,7 @@
         <v>2.6932038834951461E-2</v>
       </c>
       <c r="G41">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H41">
         <v>4725</v>
@@ -23114,7 +23114,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="G42">
-        <v>0.255</v>
+        <v>0.20400000000000001</v>
       </c>
       <c r="H42">
         <v>4725</v>
@@ -23167,7 +23167,7 @@
         <v>2.4805825242718453E-2</v>
       </c>
       <c r="G43">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H43">
         <v>4725</v>
@@ -23220,7 +23220,7 @@
         <v>4.2524271844660198E-2</v>
       </c>
       <c r="G44">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H44">
         <v>4725</v>
@@ -23273,7 +23273,7 @@
         <v>0.03</v>
       </c>
       <c r="G45">
-        <v>0.255</v>
+        <v>0.20400000000000001</v>
       </c>
       <c r="H45">
         <v>4725</v>
@@ -23326,7 +23326,7 @@
         <v>2.1262135922330099E-2</v>
       </c>
       <c r="G46">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H46">
         <v>4725</v>
@@ -23379,7 +23379,7 @@
         <v>0.03</v>
       </c>
       <c r="G47">
-        <v>0.3</v>
+        <v>0.23999999999999996</v>
       </c>
       <c r="H47">
         <v>4725</v>
@@ -23432,7 +23432,7 @@
         <v>2.1262135922330099E-2</v>
       </c>
       <c r="G48">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H48">
         <v>4725</v>
@@ -23485,7 +23485,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="G49">
-        <v>0.28000000000000003</v>
+        <v>0.22400000000000003</v>
       </c>
       <c r="H49">
         <v>4725</v>
@@ -23538,7 +23538,7 @@
         <v>2.2679611650485442E-2</v>
       </c>
       <c r="G50">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H50">
         <v>4725</v>
@@ -23591,7 +23591,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="G51">
-        <v>0.28000000000000003</v>
+        <v>0.22400000000000003</v>
       </c>
       <c r="H51">
         <v>4725</v>
@@ -23644,7 +23644,7 @@
         <v>2.4805825242718453E-2</v>
       </c>
       <c r="G52">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H52">
         <v>4725</v>
@@ -23697,7 +23697,7 @@
         <v>3.9E-2</v>
       </c>
       <c r="G53">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="H53">
         <v>4725</v>
@@ -23750,7 +23750,7 @@
         <v>2.7640776699029129E-2</v>
       </c>
       <c r="G54">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H54">
         <v>4725</v>
@@ -23803,7 +23803,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G55">
-        <v>0.28000000000000003</v>
+        <v>0.22400000000000006</v>
       </c>
       <c r="H55">
         <v>4725</v>
@@ -23856,7 +23856,7 @@
         <v>7.0873786407766995E-2</v>
       </c>
       <c r="G56">
-        <v>0.33</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="H56">
         <v>4025</v>
@@ -23909,7 +23909,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G57">
-        <v>0.3</v>
+        <v>0.24000000000000002</v>
       </c>
       <c r="H57">
         <v>4725</v>
@@ -23962,7 +23962,7 @@
         <v>2.5514563106796121E-2</v>
       </c>
       <c r="G58">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H58">
         <v>4725</v>
@@ -24015,7 +24015,7 @@
         <v>0.04</v>
       </c>
       <c r="G59">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="H59">
         <v>4725</v>
@@ -24068,7 +24068,7 @@
         <v>2.8349514563106804E-2</v>
       </c>
       <c r="G60">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H60">
         <v>4725</v>
@@ -24121,7 +24121,7 @@
         <v>0.16500000000000001</v>
       </c>
       <c r="G61">
-        <v>0.33</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="H61">
         <v>2645</v>
@@ -24174,7 +24174,7 @@
         <v>0.11</v>
       </c>
       <c r="G62">
-        <v>0.28000000000000003</v>
+        <v>0.22400000000000003</v>
       </c>
       <c r="H62">
         <v>4140</v>
@@ -24227,7 +24227,7 @@
         <v>0.11</v>
       </c>
       <c r="G63">
-        <v>0.28000000000000003</v>
+        <v>0.22400000000000003</v>
       </c>
       <c r="H63">
         <v>4140</v>
@@ -24280,7 +24280,7 @@
         <v>0.433</v>
       </c>
       <c r="G64">
-        <v>0.34</v>
+        <v>0.27200000000000002</v>
       </c>
       <c r="H64">
         <v>2000</v>
@@ -24333,7 +24333,7 @@
         <v>0.49</v>
       </c>
       <c r="G65">
-        <v>0.36</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="H65">
         <v>2000</v>
@@ -24386,7 +24386,7 @@
         <v>0.29299999999999998</v>
       </c>
       <c r="G66">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H66">
         <v>2300</v>
@@ -24439,7 +24439,7 @@
         <v>0.43</v>
       </c>
       <c r="G67">
-        <v>0.35</v>
+        <v>0.27999999999999997</v>
       </c>
       <c r="H67">
         <v>2000</v>
@@ -24492,7 +24492,7 @@
         <v>0.45</v>
       </c>
       <c r="G68">
-        <v>0.36</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="H68">
         <v>2000</v>
@@ -24545,7 +24545,7 @@
         <v>0.15</v>
       </c>
       <c r="G69">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H69">
         <v>2300</v>
@@ -24598,7 +24598,7 @@
         <v>0.15819999999999998</v>
       </c>
       <c r="G70">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H70">
         <v>2300</v>
@@ -24651,7 +24651,7 @@
         <v>0.15819999999999998</v>
       </c>
       <c r="G71">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H71">
         <v>2300</v>
@@ -24704,7 +24704,7 @@
         <v>0.15819999999999998</v>
       </c>
       <c r="G72">
-        <v>0.33</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="H72">
         <v>2300</v>
@@ -24757,7 +24757,7 @@
         <v>0.15819999999999998</v>
       </c>
       <c r="G73">
-        <v>0.33</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="H73">
         <v>2300</v>
@@ -24810,7 +24810,7 @@
         <v>0.152</v>
       </c>
       <c r="G74">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="H74">
         <v>2300</v>
@@ -24863,7 +24863,7 @@
         <v>0.158</v>
       </c>
       <c r="G75">
-        <v>0.34</v>
+        <v>0.27200000000000002</v>
       </c>
       <c r="H75">
         <v>2300</v>
@@ -24916,7 +24916,7 @@
         <v>0.15</v>
       </c>
       <c r="G76">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H76">
         <v>2300</v>
@@ -24969,7 +24969,7 @@
         <v>0.315</v>
       </c>
       <c r="G77">
-        <v>0.34</v>
+        <v>0.27200000000000002</v>
       </c>
       <c r="H77">
         <v>2000</v>
@@ -25022,7 +25022,7 @@
         <v>0.315</v>
       </c>
       <c r="G78">
-        <v>0.35</v>
+        <v>0.27999999999999997</v>
       </c>
       <c r="H78">
         <v>2000</v>
@@ -25075,7 +25075,7 @@
         <v>0.3</v>
       </c>
       <c r="G79">
-        <v>0.34</v>
+        <v>0.27200000000000002</v>
       </c>
       <c r="H79">
         <v>2300</v>
@@ -25128,7 +25128,7 @@
         <v>0.46600000000000003</v>
       </c>
       <c r="G80">
-        <v>0.39500000000000007</v>
+        <v>0.31600000000000006</v>
       </c>
       <c r="H80">
         <v>2200</v>
@@ -25181,7 +25181,7 @@
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="G81">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H81">
         <v>1150</v>
@@ -25234,7 +25234,7 @@
         <v>0.9</v>
       </c>
       <c r="G82">
-        <v>0.57999999999999996</v>
+        <v>0.46399999999999997</v>
       </c>
       <c r="H82">
         <v>1000</v>
@@ -25287,7 +25287,7 @@
         <v>0.45</v>
       </c>
       <c r="G83">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="H83">
         <v>1000</v>
@@ -25340,7 +25340,7 @@
         <v>0.45</v>
       </c>
       <c r="G84">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="H84">
         <v>1000</v>
@@ -25393,7 +25393,7 @@
         <v>0.35299999999999998</v>
       </c>
       <c r="G85">
-        <v>0.57999999999999996</v>
+        <v>0.46400000000000002</v>
       </c>
       <c r="H85">
         <v>1000</v>
@@ -25446,7 +25446,7 @@
         <v>0.36</v>
       </c>
       <c r="G86">
-        <v>0.6</v>
+        <v>0.47999999999999993</v>
       </c>
       <c r="H86">
         <v>1000</v>
@@ -25499,7 +25499,7 @@
         <v>0.12</v>
       </c>
       <c r="G87">
-        <v>0.52</v>
+        <v>0.41600000000000004</v>
       </c>
       <c r="H87">
         <v>1150</v>
@@ -25552,7 +25552,7 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="G88">
-        <v>0.52</v>
+        <v>0.41600000000000004</v>
       </c>
       <c r="H88">
         <v>1150</v>
@@ -25605,7 +25605,7 @@
         <v>0.1</v>
       </c>
       <c r="G89">
-        <v>0.52</v>
+        <v>0.41600000000000004</v>
       </c>
       <c r="H89">
         <v>1150</v>
@@ -25658,7 +25658,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G90">
-        <v>0.54500000000000004</v>
+        <v>0.43600000000000005</v>
       </c>
       <c r="H90">
         <v>1000</v>
@@ -25711,7 +25711,7 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="G91">
-        <v>0.54500000000000004</v>
+        <v>0.43600000000000005</v>
       </c>
       <c r="H91">
         <v>1000</v>
@@ -25764,7 +25764,7 @@
         <v>0.32</v>
       </c>
       <c r="G92">
-        <v>0.54500000000000004</v>
+        <v>0.43600000000000005</v>
       </c>
       <c r="H92">
         <v>1000</v>
@@ -25817,7 +25817,7 @@
         <v>0.156</v>
       </c>
       <c r="G93">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H93">
         <v>1150</v>
@@ -25870,7 +25870,7 @@
         <v>0.12</v>
       </c>
       <c r="G94">
-        <v>0.52</v>
+        <v>0.41600000000000004</v>
       </c>
       <c r="H94">
         <v>1150</v>
@@ -25923,7 +25923,7 @@
         <v>0.249</v>
       </c>
       <c r="G95">
-        <v>0.52</v>
+        <v>0.41600000000000004</v>
       </c>
       <c r="H95">
         <v>1150</v>
@@ -25976,7 +25976,7 @@
         <v>0.11799999999999999</v>
       </c>
       <c r="G96">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H96">
         <v>1150</v>
@@ -26029,7 +26029,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="G97">
-        <v>0.6</v>
+        <v>0.48000000000000004</v>
       </c>
       <c r="H97">
         <v>1000</v>
@@ -26082,7 +26082,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="G98">
-        <v>0.6</v>
+        <v>0.48000000000000004</v>
       </c>
       <c r="H98">
         <v>1000</v>
@@ -26135,7 +26135,7 @@
         <v>0.875</v>
       </c>
       <c r="G99">
-        <v>0.54500000000000004</v>
+        <v>0.43600000000000005</v>
       </c>
       <c r="H99">
         <v>1000</v>
@@ -26188,7 +26188,7 @@
         <v>0.3</v>
       </c>
       <c r="G100">
-        <v>0.56000000000000005</v>
+        <v>0.44800000000000001</v>
       </c>
       <c r="H100">
         <v>1150</v>
@@ -26241,7 +26241,7 @@
         <v>1.038</v>
       </c>
       <c r="G101">
-        <v>0.54500000000000004</v>
+        <v>0.43600000000000005</v>
       </c>
       <c r="H101">
         <v>1000</v>
@@ -26294,7 +26294,7 @@
         <v>0.12</v>
       </c>
       <c r="G102">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H102">
         <v>1150</v>
@@ -26347,7 +26347,7 @@
         <v>0.27500000000000002</v>
       </c>
       <c r="G103">
-        <v>0.52</v>
+        <v>0.41600000000000004</v>
       </c>
       <c r="H103">
         <v>1150</v>
@@ -26400,7 +26400,7 @@
         <v>0.11</v>
       </c>
       <c r="G104">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H104">
         <v>1150</v>
@@ -26453,7 +26453,7 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="G105">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H105">
         <v>1150</v>
@@ -26506,7 +26506,7 @@
         <v>0.48</v>
       </c>
       <c r="G106">
-        <v>0.54500000000000004</v>
+        <v>0.43600000000000005</v>
       </c>
       <c r="H106">
         <v>1000</v>
@@ -26559,7 +26559,7 @@
         <v>0.10100000000000001</v>
       </c>
       <c r="G107">
-        <v>0.52</v>
+        <v>0.41600000000000004</v>
       </c>
       <c r="H107">
         <v>1150</v>
@@ -26612,7 +26612,7 @@
         <v>0.10100000000000001</v>
       </c>
       <c r="G108">
-        <v>0.52</v>
+        <v>0.41600000000000004</v>
       </c>
       <c r="H108">
         <v>1150</v>
@@ -26665,7 +26665,7 @@
         <v>0.19500000000000001</v>
       </c>
       <c r="G109">
-        <v>0.52</v>
+        <v>0.41600000000000004</v>
       </c>
       <c r="H109">
         <v>1150</v>
@@ -26718,7 +26718,7 @@
         <v>0.22800000000000001</v>
       </c>
       <c r="G110">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H110">
         <v>1150</v>
@@ -26771,7 +26771,7 @@
         <v>0.68300000000000005</v>
       </c>
       <c r="G111">
-        <v>0.54500000000000004</v>
+        <v>0.436</v>
       </c>
       <c r="H111">
         <v>1000</v>
@@ -26824,7 +26824,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G112">
-        <v>0.54500000000000004</v>
+        <v>0.43600000000000005</v>
       </c>
       <c r="H112">
         <v>1000</v>
@@ -26877,7 +26877,7 @@
         <v>0.28599999999999998</v>
       </c>
       <c r="G113">
-        <v>0.56000000000000005</v>
+        <v>0.44800000000000006</v>
       </c>
       <c r="H113">
         <v>1150</v>
@@ -26930,7 +26930,7 @@
         <v>0.224</v>
       </c>
       <c r="G114">
-        <v>0.52</v>
+        <v>0.41600000000000004</v>
       </c>
       <c r="H114">
         <v>1150</v>
@@ -26983,7 +26983,7 @@
         <v>0.14099999999999999</v>
       </c>
       <c r="G115">
-        <v>0.34</v>
+        <v>0.27200000000000002</v>
       </c>
       <c r="H115">
         <v>1150</v>
@@ -27036,7 +27036,7 @@
         <v>0.499</v>
       </c>
       <c r="G116">
-        <v>0.54500000000000004</v>
+        <v>0.43600000000000005</v>
       </c>
       <c r="H116">
         <v>1000</v>
@@ -27089,7 +27089,7 @@
         <v>0.86</v>
       </c>
       <c r="G117">
-        <v>0.57999999999999996</v>
+        <v>0.46399999999999997</v>
       </c>
       <c r="H117">
         <v>1000</v>
@@ -27142,7 +27142,7 @@
         <v>0.29199999999999998</v>
       </c>
       <c r="G118">
-        <v>0.52</v>
+        <v>0.41600000000000004</v>
       </c>
       <c r="H118">
         <v>1150</v>
@@ -27195,7 +27195,7 @@
         <v>0.29199999999999998</v>
       </c>
       <c r="G119">
-        <v>0.52</v>
+        <v>0.41600000000000004</v>
       </c>
       <c r="H119">
         <v>1150</v>
@@ -27248,7 +27248,7 @@
         <v>0.40300000000000002</v>
       </c>
       <c r="G120">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="H120">
         <v>1000</v>
@@ -27301,7 +27301,7 @@
         <v>0.40300000000000002</v>
       </c>
       <c r="G121">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="H121">
         <v>1000</v>
@@ -27354,7 +27354,7 @@
         <v>0.26500000000000001</v>
       </c>
       <c r="G122">
-        <v>0.52</v>
+        <v>0.41600000000000004</v>
       </c>
       <c r="H122">
         <v>1150</v>
@@ -27407,7 +27407,7 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="G123">
-        <v>0.52</v>
+        <v>0.41600000000000004</v>
       </c>
       <c r="H123">
         <v>1150</v>
@@ -27460,7 +27460,7 @@
         <v>0.13539999999999999</v>
       </c>
       <c r="G124">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H124">
         <v>1150</v>
@@ -27513,7 +27513,7 @@
         <v>0.11</v>
       </c>
       <c r="G125">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H125">
         <v>1150</v>
@@ -27566,7 +27566,7 @@
         <v>9.8000000000000004E-2</v>
       </c>
       <c r="G126">
-        <v>0.52</v>
+        <v>0.41599999999999998</v>
       </c>
       <c r="H126">
         <v>1150</v>
@@ -27619,7 +27619,7 @@
         <v>0.1</v>
       </c>
       <c r="G127">
-        <v>0.56000000000000005</v>
+        <v>0.44800000000000006</v>
       </c>
       <c r="H127">
         <v>1150</v>
@@ -27672,7 +27672,7 @@
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="G128">
-        <v>0.57999999999999996</v>
+        <v>0.46399999999999997</v>
       </c>
       <c r="H128">
         <v>1150</v>
@@ -27725,7 +27725,7 @@
         <v>0.20399999999999999</v>
       </c>
       <c r="G129">
-        <v>0.56000000000000005</v>
+        <v>0.44800000000000006</v>
       </c>
       <c r="H129">
         <v>1150</v>
@@ -27778,7 +27778,7 @@
         <v>0.14099999999999999</v>
       </c>
       <c r="G130">
-        <v>0.34</v>
+        <v>0.27200000000000002</v>
       </c>
       <c r="H130">
         <v>1150</v>
@@ -27831,7 +27831,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="G131">
-        <v>0.52</v>
+        <v>0.41600000000000009</v>
       </c>
       <c r="H131">
         <v>1150</v>
@@ -27884,7 +27884,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="G132">
-        <v>0.56000000000000005</v>
+        <v>0.44800000000000006</v>
       </c>
       <c r="H132">
         <v>1150</v>
@@ -27937,7 +27937,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
       <c r="G133">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H133">
         <v>1150</v>
@@ -27990,7 +27990,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="G134">
-        <v>0.56000000000000005</v>
+        <v>0.44800000000000012</v>
       </c>
       <c r="H134">
         <v>1150</v>
@@ -28043,7 +28043,7 @@
         <v>0.08</v>
       </c>
       <c r="G135">
-        <v>0.26500000000000001</v>
+        <v>0.21200000000000002</v>
       </c>
       <c r="H135">
         <v>919.99999999999977</v>
@@ -28096,7 +28096,7 @@
         <v>0.10299999999999999</v>
       </c>
       <c r="G136">
-        <v>0.26500000000000001</v>
+        <v>0.21200000000000002</v>
       </c>
       <c r="H136">
         <v>919.99999999999989</v>
@@ -28149,7 +28149,7 @@
         <v>0.10299999999999999</v>
       </c>
       <c r="G137">
-        <v>0.26500000000000001</v>
+        <v>0.21200000000000002</v>
       </c>
       <c r="H137">
         <v>919.99999999999989</v>
@@ -28202,7 +28202,7 @@
         <v>0.10299999999999999</v>
       </c>
       <c r="G138">
-        <v>0.26500000000000001</v>
+        <v>0.21200000000000002</v>
       </c>
       <c r="H138">
         <v>919.99999999999989</v>
@@ -28255,7 +28255,7 @@
         <v>0.10299999999999999</v>
       </c>
       <c r="G139">
-        <v>0.26500000000000001</v>
+        <v>0.21200000000000002</v>
       </c>
       <c r="H139">
         <v>919.99999999999989</v>
@@ -28308,7 +28308,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G140">
-        <v>0.28999999999999998</v>
+        <v>0.23199999999999998</v>
       </c>
       <c r="H140">
         <v>919.99999999999989</v>
@@ -28361,7 +28361,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G141">
-        <v>0.28999999999999998</v>
+        <v>0.23199999999999998</v>
       </c>
       <c r="H141">
         <v>919.99999999999989</v>
@@ -28414,7 +28414,7 @@
         <v>0.1</v>
       </c>
       <c r="G142">
-        <v>0.28999999999999998</v>
+        <v>0.23199999999999998</v>
       </c>
       <c r="H142">
         <v>919.99999999999989</v>
@@ -28467,7 +28467,7 @@
         <v>0.1</v>
       </c>
       <c r="G143">
-        <v>0.28999999999999998</v>
+        <v>0.23199999999999998</v>
       </c>
       <c r="H143">
         <v>919.99999999999989</v>
@@ -28520,7 +28520,7 @@
         <v>0.105</v>
       </c>
       <c r="G144">
-        <v>0.31</v>
+        <v>0.248</v>
       </c>
       <c r="H144">
         <v>919.99999999999989</v>
@@ -28573,7 +28573,7 @@
         <v>0.10299999999999999</v>
       </c>
       <c r="G145">
-        <v>0.28999999999999998</v>
+        <v>0.23199999999999998</v>
       </c>
       <c r="H145">
         <v>919.99999999999989</v>
@@ -28626,7 +28626,7 @@
         <v>0.20399999999999999</v>
       </c>
       <c r="G146">
-        <v>0.31</v>
+        <v>0.248</v>
       </c>
       <c r="H146">
         <v>919.99999999999989</v>
@@ -28679,7 +28679,7 @@
         <v>0.16500000000000001</v>
       </c>
       <c r="G147">
-        <v>0.28999999999999998</v>
+        <v>0.23199999999999996</v>
       </c>
       <c r="H147">
         <v>919.99999999999977</v>
@@ -28732,7 +28732,7 @@
         <v>0.1</v>
       </c>
       <c r="G148">
-        <v>0.26500000000000001</v>
+        <v>0.21200000000000002</v>
       </c>
       <c r="H148">
         <v>919.99999999999989</v>
@@ -28785,7 +28785,7 @@
         <v>0.17</v>
       </c>
       <c r="G149">
-        <v>0.31</v>
+        <v>0.24799999999999997</v>
       </c>
       <c r="H149">
         <v>919.99999999999977</v>
@@ -28838,7 +28838,7 @@
         <v>0.09</v>
       </c>
       <c r="G150">
-        <v>0.28999999999999998</v>
+        <v>0.23199999999999998</v>
       </c>
       <c r="H150">
         <v>919.99999999999989</v>
@@ -28891,7 +28891,7 @@
         <v>0.1</v>
       </c>
       <c r="G151">
-        <v>0.26500000000000001</v>
+        <v>0.21200000000000002</v>
       </c>
       <c r="H151">
         <v>919.99999999999989</v>
@@ -28944,7 +28944,7 @@
         <v>0.22800000000000001</v>
       </c>
       <c r="G152">
-        <v>0.30999999999999994</v>
+        <v>0.248</v>
       </c>
       <c r="H152">
         <v>919.99999999999989</v>
@@ -28997,7 +28997,7 @@
         <v>0.22800000000000001</v>
       </c>
       <c r="G153">
-        <v>0.30999999999999994</v>
+        <v>0.248</v>
       </c>
       <c r="H153">
         <v>919.99999999999989</v>
@@ -29050,7 +29050,7 @@
         <v>0.15</v>
       </c>
       <c r="G154">
-        <v>0.26500000000000001</v>
+        <v>0.21200000000000002</v>
       </c>
       <c r="H154">
         <v>919.99999999999977</v>
@@ -29103,7 +29103,7 @@
         <v>0.1</v>
       </c>
       <c r="G155">
-        <v>0.26500000000000001</v>
+        <v>0.21200000000000002</v>
       </c>
       <c r="H155">
         <v>919.99999999999989</v>
@@ -29156,7 +29156,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="G156">
-        <v>0.31</v>
+        <v>0.248</v>
       </c>
       <c r="H156">
         <v>919.99999999999989</v>
@@ -29209,7 +29209,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
       <c r="G157">
-        <v>0.31</v>
+        <v>0.248</v>
       </c>
       <c r="H157">
         <v>919.99999999999989</v>
@@ -29262,7 +29262,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G158">
-        <v>0.31</v>
+        <v>0.24800000000000003</v>
       </c>
       <c r="H158">
         <v>919.99999999999977</v>
@@ -29315,7 +29315,7 @@
         <v>0.16</v>
       </c>
       <c r="G159">
-        <v>0.28999999999999998</v>
+        <v>0.23199999999999998</v>
       </c>
       <c r="H159">
         <v>919.99999999999977</v>
@@ -29368,7 +29368,7 @@
         <v>0.05</v>
       </c>
       <c r="G160">
-        <v>0.255</v>
+        <v>0.20400000000000001</v>
       </c>
       <c r="H160">
         <v>1080</v>
@@ -29421,7 +29421,7 @@
         <v>0.10199999999999999</v>
       </c>
       <c r="G161">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H161">
         <v>919.99999999999989</v>
@@ -29474,7 +29474,7 @@
         <v>0.42499999999999999</v>
       </c>
       <c r="G162">
-        <v>0.28999999999999998</v>
+        <v>0.23199999999999998</v>
       </c>
       <c r="H162">
         <v>919.99999999999989</v>
@@ -29527,7 +29527,7 @@
         <v>0.05</v>
       </c>
       <c r="G163">
-        <v>0.28000000000000003</v>
+        <v>0.22400000000000003</v>
       </c>
       <c r="H163">
         <v>1080</v>
@@ -29580,7 +29580,7 @@
         <v>0.05</v>
       </c>
       <c r="G164">
-        <v>0.28000000000000003</v>
+        <v>0.22400000000000003</v>
       </c>
       <c r="H164">
         <v>1080</v>
@@ -29633,7 +29633,7 @@
         <v>0.17</v>
       </c>
       <c r="G165">
-        <v>0.28999999999999998</v>
+        <v>0.23199999999999998</v>
       </c>
       <c r="H165">
         <v>919.99999999999977</v>
@@ -29686,7 +29686,7 @@
         <v>7.8E-2</v>
       </c>
       <c r="G166">
-        <v>0.26500000000000001</v>
+        <v>0.21200000000000002</v>
       </c>
       <c r="H166">
         <v>919.99999999999977</v>
@@ -29739,7 +29739,7 @@
         <v>5.5E-2</v>
       </c>
       <c r="G167">
-        <v>0.28999999999999998</v>
+        <v>0.23199999999999998</v>
       </c>
       <c r="H167">
         <v>919.99999999999989</v>
@@ -29792,7 +29792,7 @@
         <v>0.12</v>
       </c>
       <c r="G168">
-        <v>0.26500000000000001</v>
+        <v>0.21200000000000002</v>
       </c>
       <c r="H168">
         <v>919.99999999999989</v>
@@ -29845,7 +29845,7 @@
         <v>0.15</v>
       </c>
       <c r="G169">
-        <v>0.31</v>
+        <v>0.24800000000000003</v>
       </c>
       <c r="H169">
         <v>1380</v>
@@ -29898,7 +29898,7 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="G170">
-        <v>0.33</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="H170">
         <v>1200</v>
@@ -29951,7 +29951,7 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="G171">
-        <v>0.33</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="H171">
         <v>1200</v>
@@ -30004,7 +30004,7 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="G172">
-        <v>0.33</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="H172">
         <v>1200</v>
@@ -30057,7 +30057,7 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="G173">
-        <v>0.33</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="H173">
         <v>1200</v>
@@ -30110,7 +30110,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="G174">
-        <v>0.34</v>
+        <v>0.27200000000000002</v>
       </c>
       <c r="H174">
         <v>1380</v>
@@ -30163,7 +30163,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="G175">
-        <v>0.28999999999999998</v>
+        <v>0.23199999999999998</v>
       </c>
       <c r="H175">
         <v>1380</v>
@@ -30216,7 +30216,7 @@
         <v>0.42199999999999999</v>
       </c>
       <c r="G176">
-        <v>0.36499999999999999</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="H176">
         <v>1200</v>
@@ -30269,7 +30269,7 @@
         <v>0.46600000000000003</v>
       </c>
       <c r="G177">
-        <v>0.36499999999999999</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="H177">
         <v>1200</v>
@@ -30322,7 +30322,7 @@
         <v>0.38500000000000001</v>
       </c>
       <c r="G178">
-        <v>0.36499999999999999</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="H178">
         <v>1200</v>
@@ -30375,7 +30375,7 @@
         <v>0.46300000000000002</v>
       </c>
       <c r="G179">
-        <v>0.36499999999999999</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="H179">
         <v>1200</v>
@@ -30428,7 +30428,7 @@
         <v>0.39</v>
       </c>
       <c r="G180">
-        <v>0.36499999999999999</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="H180">
         <v>1200</v>
@@ -30481,7 +30481,7 @@
         <v>0.39</v>
       </c>
       <c r="G181">
-        <v>0.36499999999999999</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="H181">
         <v>1200</v>
@@ -30534,7 +30534,7 @@
         <v>0.4032</v>
       </c>
       <c r="G182">
-        <v>0.36500000000000005</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="H182">
         <v>1200</v>
@@ -30587,7 +30587,7 @@
         <v>0.155</v>
       </c>
       <c r="G183">
-        <v>0.34499999999999997</v>
+        <v>0.27599999999999997</v>
       </c>
       <c r="H183">
         <v>1380</v>
@@ -30640,7 +30640,7 @@
         <v>0.113</v>
       </c>
       <c r="G184">
-        <v>0.34499999999999997</v>
+        <v>0.27599999999999997</v>
       </c>
       <c r="H184">
         <v>1380</v>
@@ -30693,7 +30693,7 @@
         <v>0.217</v>
       </c>
       <c r="G185">
-        <v>0.33808755760368664</v>
+        <v>0.27047004608294933</v>
       </c>
       <c r="H185">
         <v>1545.8986175115208</v>
@@ -30746,7 +30746,7 @@
         <v>0.05</v>
       </c>
       <c r="G186">
-        <v>0.33500000000000002</v>
+        <v>0.26800000000000002</v>
       </c>
       <c r="H186">
         <v>1620</v>
@@ -30799,7 +30799,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="G187">
-        <v>0.34499999999999997</v>
+        <v>0.27599999999999997</v>
       </c>
       <c r="H187">
         <v>1380</v>
@@ -44006,7 +44006,7 @@
         <v>609</v>
       </c>
       <c r="P447" t="s">
-        <v>857</v>
+        <v>732</v>
       </c>
       <c r="Q447" t="s">
         <v>728</v>
@@ -44059,7 +44059,7 @@
         <v>609</v>
       </c>
       <c r="P448" t="s">
-        <v>732</v>
+        <v>857</v>
       </c>
       <c r="Q448" t="s">
         <v>728</v>
@@ -44568,7 +44568,7 @@
         <v>0.1</v>
       </c>
       <c r="G458">
-        <v>0.255</v>
+        <v>0.20400000000000001</v>
       </c>
       <c r="H458">
         <v>1035</v>
@@ -44621,7 +44621,7 @@
         <v>0.1</v>
       </c>
       <c r="G459">
-        <v>0.255</v>
+        <v>0.20400000000000001</v>
       </c>
       <c r="H459">
         <v>1035</v>
@@ -44674,7 +44674,7 @@
         <v>0.1</v>
       </c>
       <c r="G460">
-        <v>0.255</v>
+        <v>0.20400000000000001</v>
       </c>
       <c r="H460">
         <v>1035</v>
@@ -44727,7 +44727,7 @@
         <v>0.1</v>
       </c>
       <c r="G461">
-        <v>0.255</v>
+        <v>0.20400000000000001</v>
       </c>
       <c r="H461">
         <v>1035</v>
@@ -44780,7 +44780,7 @@
         <v>0.1</v>
       </c>
       <c r="G462">
-        <v>0.255</v>
+        <v>0.20400000000000001</v>
       </c>
       <c r="H462">
         <v>1035</v>
@@ -44833,7 +44833,7 @@
         <v>0.05</v>
       </c>
       <c r="G463">
-        <v>0.27</v>
+        <v>0.21600000000000003</v>
       </c>
       <c r="H463">
         <v>1215</v>
@@ -44886,7 +44886,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="G464">
-        <v>0.30499999999999999</v>
+        <v>0.24399999999999999</v>
       </c>
       <c r="H464">
         <v>1150</v>
@@ -44939,7 +44939,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="G465">
-        <v>0.32500000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="H465">
         <v>1150</v>
@@ -44992,7 +44992,7 @@
         <v>0.1633</v>
       </c>
       <c r="G466">
-        <v>0.28999999999999998</v>
+        <v>0.23199999999999996</v>
       </c>
       <c r="H466">
         <v>1494.9999999999998</v>
@@ -45045,7 +45045,7 @@
         <v>0.1633</v>
       </c>
       <c r="G467">
-        <v>0.28999999999999998</v>
+        <v>0.23199999999999996</v>
       </c>
       <c r="H467">
         <v>1494.9999999999998</v>
@@ -45098,7 +45098,7 @@
         <v>0.1633</v>
       </c>
       <c r="G468">
-        <v>0.28999999999999998</v>
+        <v>0.23199999999999996</v>
       </c>
       <c r="H468">
         <v>1494.9999999999998</v>
@@ -45151,7 +45151,7 @@
         <v>0.35</v>
       </c>
       <c r="G469">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H469">
         <v>1300</v>
@@ -45204,7 +45204,7 @@
         <v>0.35</v>
       </c>
       <c r="G470">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H470">
         <v>1300</v>
@@ -45257,7 +45257,7 @@
         <v>0.35</v>
       </c>
       <c r="G471">
-        <v>0.32</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="H471">
         <v>1300</v>
@@ -45316,7 +45316,7 @@
         <v>33</v>
       </c>
       <c r="L472">
-        <v>0.20066638501093173</v>
+        <v>0.20066638501093176</v>
       </c>
       <c r="N472" t="s">
         <v>726</v>
@@ -45363,7 +45363,7 @@
         <v>33</v>
       </c>
       <c r="L473">
-        <v>0.20066638501093173</v>
+        <v>0.20066638501093176</v>
       </c>
       <c r="N473" t="s">
         <v>726</v>
@@ -45410,7 +45410,7 @@
         <v>33</v>
       </c>
       <c r="L474">
-        <v>0.20066638501093173</v>
+        <v>0.20066638501093176</v>
       </c>
       <c r="N474" t="s">
         <v>726</v>
@@ -46147,7 +46147,7 @@
         <v>677</v>
       </c>
       <c r="P487" t="s">
-        <v>732</v>
+        <v>857</v>
       </c>
       <c r="Q487" t="s">
         <v>728</v>
@@ -46203,7 +46203,7 @@
         <v>677</v>
       </c>
       <c r="P488" t="s">
-        <v>857</v>
+        <v>732</v>
       </c>
       <c r="Q488" t="s">
         <v>728</v>
@@ -52893,7 +52893,7 @@
         <v>47</v>
       </c>
       <c r="L662">
-        <v>0.35543377524859937</v>
+        <v>0.35543377524859943</v>
       </c>
     </row>
     <row r="663" spans="2:12" x14ac:dyDescent="0.45">
@@ -52928,7 +52928,7 @@
         <v>45</v>
       </c>
       <c r="L663">
-        <v>0.35543377524859937</v>
+        <v>0.35543377524859943</v>
       </c>
     </row>
     <row r="664" spans="2:12" x14ac:dyDescent="0.45">
@@ -53497,7 +53497,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9064EB2-7E7A-4FDB-8958-921B70B3BB5B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9F4F3AD-70B6-40C2-82B7-746BC03FE446}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_CAN_grids_kan/vt_vervestacks_CAN_v1.xlsx
+++ b/VerveStacks_CAN_grids_kan/vt_vervestacks_CAN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5B8F0D0-0C5C-43A0-8FC9-94BBDFE37349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CAFB607C-C0A2-4C9D-AE3E-BDC82AC83B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6D4F8A64-A361-401E-B3D4-77D04063BCB9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{35E67FDF-80B3-47C0-9A0F-275E0FEB12DC}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -5060,7 +5060,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13BF747E-889B-4915-BCCE-9C765CC89BB2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C9BC0F5-C438-4876-8973-F9E7C43636D7}">
   <dimension ref="B9:O14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5283,7 +5283,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C370C97-45E9-4217-B196-7B39EA393324}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1A523E-2E2E-4C21-A83D-E3F4A87FDF5E}">
   <dimension ref="B9:T167"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6258,7 +6258,7 @@
         <v>21</v>
       </c>
       <c r="E27">
-        <v>8.0256000000000022E-2</v>
+        <v>7.5240000000000015E-2</v>
       </c>
       <c r="F27">
         <v>3583</v>
@@ -6314,7 +6314,7 @@
         <v>86</v>
       </c>
       <c r="E28">
-        <v>6.8096000000000018E-2</v>
+        <v>6.3840000000000022E-2</v>
       </c>
       <c r="F28">
         <v>3583</v>
@@ -6370,7 +6370,7 @@
         <v>88</v>
       </c>
       <c r="E29">
-        <v>0.18876800000000002</v>
+        <v>0.17697000000000002</v>
       </c>
       <c r="F29">
         <v>2445</v>
@@ -6426,7 +6426,7 @@
         <v>90</v>
       </c>
       <c r="E30">
-        <v>0.19987200000000002</v>
+        <v>0.18738000000000002</v>
       </c>
       <c r="F30">
         <v>2445</v>
@@ -6482,7 +6482,7 @@
         <v>86</v>
       </c>
       <c r="E31">
-        <v>7.7824000000000018E-2</v>
+        <v>7.2959999999999997E-2</v>
       </c>
       <c r="F31">
         <v>3583</v>
@@ -6538,7 +6538,7 @@
         <v>93</v>
       </c>
       <c r="E32">
-        <v>0.19431999999999999</v>
+        <v>0.18217499999999998</v>
       </c>
       <c r="F32">
         <v>2445</v>
@@ -6594,7 +6594,7 @@
         <v>93</v>
       </c>
       <c r="E33">
-        <v>0.19987200000000002</v>
+        <v>0.18738000000000002</v>
       </c>
       <c r="F33">
         <v>2445</v>
@@ -6650,7 +6650,7 @@
         <v>67</v>
       </c>
       <c r="E34">
-        <v>7.7824000000000018E-2</v>
+        <v>7.2960000000000011E-2</v>
       </c>
       <c r="F34">
         <v>3583</v>
@@ -6706,7 +6706,7 @@
         <v>21</v>
       </c>
       <c r="E35">
-        <v>7.7824000000000018E-2</v>
+        <v>7.2960000000000011E-2</v>
       </c>
       <c r="F35">
         <v>3583</v>
@@ -6762,7 +6762,7 @@
         <v>21</v>
       </c>
       <c r="E36">
-        <v>7.7824000000000018E-2</v>
+        <v>7.2960000000000011E-2</v>
       </c>
       <c r="F36">
         <v>3583</v>
@@ -6818,7 +6818,7 @@
         <v>21</v>
       </c>
       <c r="E37">
-        <v>8.0256000000000022E-2</v>
+        <v>7.5240000000000015E-2</v>
       </c>
       <c r="F37">
         <v>3583</v>
@@ -6874,7 +6874,7 @@
         <v>21</v>
       </c>
       <c r="E38">
-        <v>8.0256000000000022E-2</v>
+        <v>7.5240000000000015E-2</v>
       </c>
       <c r="F38">
         <v>3583</v>
@@ -6930,7 +6930,7 @@
         <v>101</v>
       </c>
       <c r="E39">
-        <v>7.2960000000000011E-2</v>
+        <v>6.8400000000000002E-2</v>
       </c>
       <c r="F39">
         <v>3583</v>
@@ -6986,7 +6986,7 @@
         <v>101</v>
       </c>
       <c r="E40">
-        <v>8.2688000000000025E-2</v>
+        <v>7.7520000000000019E-2</v>
       </c>
       <c r="F40">
         <v>3583</v>
@@ -7042,7 +7042,7 @@
         <v>21</v>
       </c>
       <c r="E41">
-        <v>7.7824000000000018E-2</v>
+        <v>7.2960000000000011E-2</v>
       </c>
       <c r="F41">
         <v>3583</v>
@@ -7098,7 +7098,7 @@
         <v>105</v>
       </c>
       <c r="E42">
-        <v>8.2688000000000025E-2</v>
+        <v>7.7520000000000019E-2</v>
       </c>
       <c r="F42">
         <v>3583</v>
@@ -7154,7 +7154,7 @@
         <v>105</v>
       </c>
       <c r="E43">
-        <v>8.5120000000000001E-2</v>
+        <v>7.980000000000001E-2</v>
       </c>
       <c r="F43">
         <v>3583</v>
@@ -7210,7 +7210,7 @@
         <v>86</v>
       </c>
       <c r="E44">
-        <v>8.2688000000000025E-2</v>
+        <v>7.7520000000000019E-2</v>
       </c>
       <c r="F44">
         <v>3583</v>
@@ -7266,19 +7266,19 @@
         <v>93</v>
       </c>
       <c r="E45">
-        <v>0.23068000000000005</v>
+        <v>0.20559750000000002</v>
       </c>
       <c r="F45">
-        <v>2200</v>
+        <v>2445</v>
       </c>
       <c r="G45">
-        <v>27.7</v>
+        <v>30.4</v>
       </c>
       <c r="H45">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="I45">
-        <v>0.74765000000000004</v>
+        <v>0.72770000000000001</v>
       </c>
       <c r="J45" t="s">
         <v>108</v>
@@ -7322,7 +7322,7 @@
         <v>111</v>
       </c>
       <c r="E46">
-        <v>0.35</v>
+        <v>0.328125</v>
       </c>
       <c r="F46">
         <v>1365</v>
@@ -7378,7 +7378,7 @@
         <v>113</v>
       </c>
       <c r="E47">
-        <v>0.40599999999999992</v>
+        <v>0.38062499999999994</v>
       </c>
       <c r="F47">
         <v>1365</v>
@@ -7434,7 +7434,7 @@
         <v>115</v>
       </c>
       <c r="E48">
-        <v>0.42</v>
+        <v>0.39374999999999993</v>
       </c>
       <c r="F48">
         <v>1365</v>
@@ -7490,7 +7490,7 @@
         <v>115</v>
       </c>
       <c r="E49">
-        <v>0.42</v>
+        <v>0.39374999999999993</v>
       </c>
       <c r="F49">
         <v>1365</v>
@@ -7546,7 +7546,7 @@
         <v>105</v>
       </c>
       <c r="E50">
-        <v>0.40600000000000003</v>
+        <v>0.38062499999999994</v>
       </c>
       <c r="F50">
         <v>1365</v>
@@ -7602,7 +7602,7 @@
         <v>105</v>
       </c>
       <c r="E51">
-        <v>0.41999999999999993</v>
+        <v>0.39374999999999993</v>
       </c>
       <c r="F51">
         <v>1365</v>
@@ -7658,7 +7658,7 @@
         <v>120</v>
       </c>
       <c r="E52">
-        <v>0.36400000000000005</v>
+        <v>0.34125</v>
       </c>
       <c r="F52">
         <v>1365</v>
@@ -7714,7 +7714,7 @@
         <v>122</v>
       </c>
       <c r="E53">
-        <v>0.36400000000000005</v>
+        <v>0.34125</v>
       </c>
       <c r="F53">
         <v>1365</v>
@@ -7770,7 +7770,7 @@
         <v>67</v>
       </c>
       <c r="E54">
-        <v>0.36400000000000005</v>
+        <v>0.34125</v>
       </c>
       <c r="F54">
         <v>1365</v>
@@ -7826,7 +7826,7 @@
         <v>125</v>
       </c>
       <c r="E55">
-        <v>0.38150000000000006</v>
+        <v>0.35765625000000006</v>
       </c>
       <c r="F55">
         <v>1365</v>
@@ -7882,7 +7882,7 @@
         <v>111</v>
       </c>
       <c r="E56">
-        <v>0.38150000000000006</v>
+        <v>0.35765625000000006</v>
       </c>
       <c r="F56">
         <v>1365</v>
@@ -7938,7 +7938,7 @@
         <v>120</v>
       </c>
       <c r="E57">
-        <v>0.38150000000000006</v>
+        <v>0.35765625000000006</v>
       </c>
       <c r="F57">
         <v>1365</v>
@@ -7994,7 +7994,7 @@
         <v>129</v>
       </c>
       <c r="E58">
-        <v>0.35</v>
+        <v>0.328125</v>
       </c>
       <c r="F58">
         <v>1365</v>
@@ -8050,7 +8050,7 @@
         <v>131</v>
       </c>
       <c r="E59">
-        <v>0.36400000000000005</v>
+        <v>0.34125</v>
       </c>
       <c r="F59">
         <v>1365</v>
@@ -8106,7 +8106,7 @@
         <v>133</v>
       </c>
       <c r="E60">
-        <v>0.36400000000000005</v>
+        <v>0.34125</v>
       </c>
       <c r="F60">
         <v>1365</v>
@@ -8162,7 +8162,7 @@
         <v>135</v>
       </c>
       <c r="E61">
-        <v>0.35</v>
+        <v>0.328125</v>
       </c>
       <c r="F61">
         <v>1365</v>
@@ -8218,7 +8218,7 @@
         <v>93</v>
       </c>
       <c r="E62">
-        <v>0.42</v>
+        <v>0.39374999999999993</v>
       </c>
       <c r="F62">
         <v>1365</v>
@@ -8274,7 +8274,7 @@
         <v>93</v>
       </c>
       <c r="E63">
-        <v>0.42</v>
+        <v>0.39374999999999993</v>
       </c>
       <c r="F63">
         <v>1365</v>
@@ -8330,7 +8330,7 @@
         <v>139</v>
       </c>
       <c r="E64">
-        <v>0.38150000000000006</v>
+        <v>0.35765625000000006</v>
       </c>
       <c r="F64">
         <v>1365</v>
@@ -8386,7 +8386,7 @@
         <v>141</v>
       </c>
       <c r="E65">
-        <v>0.39200000000000002</v>
+        <v>0.36749999999999999</v>
       </c>
       <c r="F65">
         <v>1365</v>
@@ -8442,7 +8442,7 @@
         <v>111</v>
       </c>
       <c r="E66">
-        <v>0.38150000000000006</v>
+        <v>0.35765625000000006</v>
       </c>
       <c r="F66">
         <v>1365</v>
@@ -8498,7 +8498,7 @@
         <v>144</v>
       </c>
       <c r="E67">
-        <v>0.35</v>
+        <v>0.328125</v>
       </c>
       <c r="F67">
         <v>1365</v>
@@ -8554,7 +8554,7 @@
         <v>146</v>
       </c>
       <c r="E68">
-        <v>0.36400000000000005</v>
+        <v>0.34125</v>
       </c>
       <c r="F68">
         <v>1365</v>
@@ -8610,7 +8610,7 @@
         <v>113</v>
       </c>
       <c r="E69">
-        <v>0.35</v>
+        <v>0.328125</v>
       </c>
       <c r="F69">
         <v>1365</v>
@@ -8666,7 +8666,7 @@
         <v>144</v>
       </c>
       <c r="E70">
-        <v>0.35</v>
+        <v>0.328125</v>
       </c>
       <c r="F70">
         <v>1365</v>
@@ -8722,7 +8722,7 @@
         <v>150</v>
       </c>
       <c r="E71">
-        <v>0.38150000000000006</v>
+        <v>0.35765625000000006</v>
       </c>
       <c r="F71">
         <v>1365</v>
@@ -8778,7 +8778,7 @@
         <v>152</v>
       </c>
       <c r="E72">
-        <v>0.36400000000000005</v>
+        <v>0.34125</v>
       </c>
       <c r="F72">
         <v>1365</v>
@@ -8834,7 +8834,7 @@
         <v>152</v>
       </c>
       <c r="E73">
-        <v>0.36400000000000005</v>
+        <v>0.34125</v>
       </c>
       <c r="F73">
         <v>1365</v>
@@ -8890,7 +8890,7 @@
         <v>155</v>
       </c>
       <c r="E74">
-        <v>0.36400000000000005</v>
+        <v>0.34124999999999994</v>
       </c>
       <c r="F74">
         <v>1365</v>
@@ -8946,7 +8946,7 @@
         <v>133</v>
       </c>
       <c r="E75">
-        <v>0.35</v>
+        <v>0.328125</v>
       </c>
       <c r="F75">
         <v>1365</v>
@@ -9002,7 +9002,7 @@
         <v>158</v>
       </c>
       <c r="E76">
-        <v>0.38150000000000001</v>
+        <v>0.35765625000000006</v>
       </c>
       <c r="F76">
         <v>1365</v>
@@ -9058,7 +9058,7 @@
         <v>160</v>
       </c>
       <c r="E77">
-        <v>0.38150000000000006</v>
+        <v>0.35765625000000006</v>
       </c>
       <c r="F77">
         <v>1365</v>
@@ -9114,7 +9114,7 @@
         <v>133</v>
       </c>
       <c r="E78">
-        <v>0.39200000000000002</v>
+        <v>0.36749999999999999</v>
       </c>
       <c r="F78">
         <v>1365</v>
@@ -9170,7 +9170,7 @@
         <v>163</v>
       </c>
       <c r="E79">
-        <v>0.36400000000000005</v>
+        <v>0.34125</v>
       </c>
       <c r="F79">
         <v>1365</v>
@@ -9226,7 +9226,7 @@
         <v>133</v>
       </c>
       <c r="E80">
-        <v>0.23800000000000002</v>
+        <v>0.22312499999999999</v>
       </c>
       <c r="F80">
         <v>1365</v>
@@ -9282,7 +9282,7 @@
         <v>141</v>
       </c>
       <c r="E81">
-        <v>0.38150000000000006</v>
+        <v>0.35765625000000006</v>
       </c>
       <c r="F81">
         <v>1365</v>
@@ -9338,7 +9338,7 @@
         <v>167</v>
       </c>
       <c r="E82">
-        <v>0.40599999999999992</v>
+        <v>0.38062499999999994</v>
       </c>
       <c r="F82">
         <v>1365</v>
@@ -9394,7 +9394,7 @@
         <v>141</v>
       </c>
       <c r="E83">
-        <v>0.36400000000000005</v>
+        <v>0.34125</v>
       </c>
       <c r="F83">
         <v>1365</v>
@@ -9450,7 +9450,7 @@
         <v>141</v>
       </c>
       <c r="E84">
-        <v>0.36400000000000005</v>
+        <v>0.34125</v>
       </c>
       <c r="F84">
         <v>1365</v>
@@ -9506,7 +9506,7 @@
         <v>163</v>
       </c>
       <c r="E85">
-        <v>0.42</v>
+        <v>0.39374999999999999</v>
       </c>
       <c r="F85">
         <v>1365</v>
@@ -9562,7 +9562,7 @@
         <v>163</v>
       </c>
       <c r="E86">
-        <v>0.42</v>
+        <v>0.39374999999999999</v>
       </c>
       <c r="F86">
         <v>1365</v>
@@ -9618,7 +9618,7 @@
         <v>173</v>
       </c>
       <c r="E87">
-        <v>0.36400000000000005</v>
+        <v>0.34125</v>
       </c>
       <c r="F87">
         <v>1365</v>
@@ -9674,7 +9674,7 @@
         <v>139</v>
       </c>
       <c r="E88">
-        <v>0.36400000000000005</v>
+        <v>0.34125</v>
       </c>
       <c r="F88">
         <v>1365</v>
@@ -9730,7 +9730,7 @@
         <v>111</v>
       </c>
       <c r="E89">
-        <v>0.35</v>
+        <v>0.328125</v>
       </c>
       <c r="F89">
         <v>1365</v>
@@ -9786,7 +9786,7 @@
         <v>35</v>
       </c>
       <c r="E90">
-        <v>0.35</v>
+        <v>0.328125</v>
       </c>
       <c r="F90">
         <v>1365</v>
@@ -9842,7 +9842,7 @@
         <v>178</v>
       </c>
       <c r="E91">
-        <v>0.36399999999999999</v>
+        <v>0.34125</v>
       </c>
       <c r="F91">
         <v>1365</v>
@@ -9898,7 +9898,7 @@
         <v>180</v>
       </c>
       <c r="E92">
-        <v>0.39200000000000002</v>
+        <v>0.36750000000000005</v>
       </c>
       <c r="F92">
         <v>1365</v>
@@ -9954,7 +9954,7 @@
         <v>67</v>
       </c>
       <c r="E93">
-        <v>0.40599999999999992</v>
+        <v>0.38062499999999994</v>
       </c>
       <c r="F93">
         <v>1365</v>
@@ -10010,7 +10010,7 @@
         <v>133</v>
       </c>
       <c r="E94">
-        <v>0.39200000000000002</v>
+        <v>0.36749999999999999</v>
       </c>
       <c r="F94">
         <v>1365</v>
@@ -10066,7 +10066,7 @@
         <v>133</v>
       </c>
       <c r="E95">
-        <v>0.23800000000000002</v>
+        <v>0.22312499999999999</v>
       </c>
       <c r="F95">
         <v>1365</v>
@@ -10122,7 +10122,7 @@
         <v>185</v>
       </c>
       <c r="E96">
-        <v>0.39200000000000002</v>
+        <v>0.36749999999999999</v>
       </c>
       <c r="F96">
         <v>1365</v>
@@ -10178,7 +10178,7 @@
         <v>187</v>
       </c>
       <c r="E97">
-        <v>0.35</v>
+        <v>0.328125</v>
       </c>
       <c r="F97">
         <v>1365</v>
@@ -10234,7 +10234,7 @@
         <v>189</v>
       </c>
       <c r="E98">
-        <v>0.39200000000000013</v>
+        <v>0.36749999999999999</v>
       </c>
       <c r="F98">
         <v>1365</v>
@@ -10290,7 +10290,7 @@
         <v>155</v>
       </c>
       <c r="E99">
-        <v>0.1855</v>
+        <v>0.17390625000000001</v>
       </c>
       <c r="F99">
         <v>1365</v>
@@ -10346,7 +10346,7 @@
         <v>125</v>
       </c>
       <c r="E100">
-        <v>0.1855</v>
+        <v>0.17390625000000001</v>
       </c>
       <c r="F100">
         <v>1365</v>
@@ -10402,7 +10402,7 @@
         <v>125</v>
       </c>
       <c r="E101">
-        <v>0.1855</v>
+        <v>0.17390625000000001</v>
       </c>
       <c r="F101">
         <v>1365</v>
@@ -10458,7 +10458,7 @@
         <v>125</v>
       </c>
       <c r="E102">
-        <v>0.1855</v>
+        <v>0.17390625000000001</v>
       </c>
       <c r="F102">
         <v>1365</v>
@@ -10514,7 +10514,7 @@
         <v>125</v>
       </c>
       <c r="E103">
-        <v>0.1855</v>
+        <v>0.17390625000000001</v>
       </c>
       <c r="F103">
         <v>1365</v>
@@ -10570,7 +10570,7 @@
         <v>86</v>
       </c>
       <c r="E104">
-        <v>0.20299999999999996</v>
+        <v>0.19031249999999997</v>
       </c>
       <c r="F104">
         <v>1365</v>
@@ -10626,7 +10626,7 @@
         <v>86</v>
       </c>
       <c r="E105">
-        <v>0.20299999999999996</v>
+        <v>0.19031249999999997</v>
       </c>
       <c r="F105">
         <v>1365</v>
@@ -10682,7 +10682,7 @@
         <v>198</v>
       </c>
       <c r="E106">
-        <v>0.20299999999999996</v>
+        <v>0.19031249999999997</v>
       </c>
       <c r="F106">
         <v>1365</v>
@@ -10738,7 +10738,7 @@
         <v>198</v>
       </c>
       <c r="E107">
-        <v>0.20299999999999996</v>
+        <v>0.19031249999999997</v>
       </c>
       <c r="F107">
         <v>1365</v>
@@ -10794,7 +10794,7 @@
         <v>67</v>
       </c>
       <c r="E108">
-        <v>0.217</v>
+        <v>0.20343749999999999</v>
       </c>
       <c r="F108">
         <v>1365</v>
@@ -10850,7 +10850,7 @@
         <v>202</v>
       </c>
       <c r="E109">
-        <v>0.20299999999999996</v>
+        <v>0.19031249999999997</v>
       </c>
       <c r="F109">
         <v>1365</v>
@@ -10906,7 +10906,7 @@
         <v>67</v>
       </c>
       <c r="E110">
-        <v>0.217</v>
+        <v>0.20343749999999999</v>
       </c>
       <c r="F110">
         <v>1365</v>
@@ -10962,7 +10962,7 @@
         <v>205</v>
       </c>
       <c r="E111">
-        <v>0.20299999999999996</v>
+        <v>0.19031249999999997</v>
       </c>
       <c r="F111">
         <v>1365</v>
@@ -11018,7 +11018,7 @@
         <v>207</v>
       </c>
       <c r="E112">
-        <v>0.1855</v>
+        <v>0.17390625000000001</v>
       </c>
       <c r="F112">
         <v>1365</v>
@@ -11074,7 +11074,7 @@
         <v>207</v>
       </c>
       <c r="E113">
-        <v>0.21699999999999997</v>
+        <v>0.20343749999999999</v>
       </c>
       <c r="F113">
         <v>1365</v>
@@ -11130,7 +11130,7 @@
         <v>141</v>
       </c>
       <c r="E114">
-        <v>0.20299999999999996</v>
+        <v>0.19031249999999997</v>
       </c>
       <c r="F114">
         <v>1365</v>
@@ -11186,7 +11186,7 @@
         <v>61</v>
       </c>
       <c r="E115">
-        <v>0.1855</v>
+        <v>0.17390625000000001</v>
       </c>
       <c r="F115">
         <v>1365</v>
@@ -11242,7 +11242,7 @@
         <v>160</v>
       </c>
       <c r="E116">
-        <v>0.217</v>
+        <v>0.20343749999999999</v>
       </c>
       <c r="F116">
         <v>1365</v>
@@ -11298,7 +11298,7 @@
         <v>160</v>
       </c>
       <c r="E117">
-        <v>0.217</v>
+        <v>0.20343749999999999</v>
       </c>
       <c r="F117">
         <v>1365</v>
@@ -11354,7 +11354,7 @@
         <v>61</v>
       </c>
       <c r="E118">
-        <v>0.1855</v>
+        <v>0.17390625000000001</v>
       </c>
       <c r="F118">
         <v>1365</v>
@@ -11410,7 +11410,7 @@
         <v>61</v>
       </c>
       <c r="E119">
-        <v>0.1855</v>
+        <v>0.17390625000000001</v>
       </c>
       <c r="F119">
         <v>1365</v>
@@ -11466,7 +11466,7 @@
         <v>216</v>
       </c>
       <c r="E120">
-        <v>0.217</v>
+        <v>0.20343749999999997</v>
       </c>
       <c r="F120">
         <v>1365</v>
@@ -11522,7 +11522,7 @@
         <v>189</v>
       </c>
       <c r="E121">
-        <v>0.217</v>
+        <v>0.20343749999999999</v>
       </c>
       <c r="F121">
         <v>1365</v>
@@ -11578,7 +11578,7 @@
         <v>216</v>
       </c>
       <c r="E122">
-        <v>0.21700000000000003</v>
+        <v>0.20343749999999999</v>
       </c>
       <c r="F122">
         <v>1365</v>
@@ -11634,7 +11634,7 @@
         <v>220</v>
       </c>
       <c r="E123">
-        <v>0.20299999999999996</v>
+        <v>0.19031249999999997</v>
       </c>
       <c r="F123">
         <v>1365</v>
@@ -11690,7 +11690,7 @@
         <v>222</v>
       </c>
       <c r="E124">
-        <v>0.17850000000000002</v>
+        <v>0.16734375000000001</v>
       </c>
       <c r="F124">
         <v>1365</v>
@@ -11746,7 +11746,7 @@
         <v>224</v>
       </c>
       <c r="E125">
-        <v>0.22400000000000003</v>
+        <v>0.21</v>
       </c>
       <c r="F125">
         <v>1365</v>
@@ -11802,7 +11802,7 @@
         <v>226</v>
       </c>
       <c r="E126">
-        <v>0.20299999999999996</v>
+        <v>0.19031249999999997</v>
       </c>
       <c r="F126">
         <v>1365</v>
@@ -11858,7 +11858,7 @@
         <v>67</v>
       </c>
       <c r="E127">
-        <v>0.19600000000000001</v>
+        <v>0.18375000000000002</v>
       </c>
       <c r="F127">
         <v>1365</v>
@@ -11914,7 +11914,7 @@
         <v>207</v>
       </c>
       <c r="E128">
-        <v>0.20299999999999996</v>
+        <v>0.19031249999999997</v>
       </c>
       <c r="F128">
         <v>1365</v>
@@ -11970,7 +11970,7 @@
         <v>133</v>
       </c>
       <c r="E129">
-        <v>0.1855</v>
+        <v>0.17390625000000001</v>
       </c>
       <c r="F129">
         <v>1365</v>
@@ -12026,7 +12026,7 @@
         <v>231</v>
       </c>
       <c r="E130">
-        <v>0.20299999999999996</v>
+        <v>0.19031249999999997</v>
       </c>
       <c r="F130">
         <v>1365</v>
@@ -12082,7 +12082,7 @@
         <v>189</v>
       </c>
       <c r="E131">
-        <v>0.1855</v>
+        <v>0.17390625000000001</v>
       </c>
       <c r="F131">
         <v>1365</v>
@@ -12138,7 +12138,7 @@
         <v>67</v>
       </c>
       <c r="E132">
-        <v>0.21700000000000003</v>
+        <v>0.20343749999999999</v>
       </c>
       <c r="F132">
         <v>1365</v>
@@ -12194,7 +12194,7 @@
         <v>113</v>
       </c>
       <c r="E133">
-        <v>0.23100000000000001</v>
+        <v>0.21656249999999999</v>
       </c>
       <c r="F133">
         <v>1365</v>
@@ -12250,7 +12250,7 @@
         <v>113</v>
       </c>
       <c r="E134">
-        <v>0.23100000000000001</v>
+        <v>0.21656249999999999</v>
       </c>
       <c r="F134">
         <v>1365</v>
@@ -12306,7 +12306,7 @@
         <v>113</v>
       </c>
       <c r="E135">
-        <v>0.23100000000000001</v>
+        <v>0.21656249999999999</v>
       </c>
       <c r="F135">
         <v>1365</v>
@@ -12362,7 +12362,7 @@
         <v>113</v>
       </c>
       <c r="E136">
-        <v>0.23100000000000001</v>
+        <v>0.21656249999999999</v>
       </c>
       <c r="F136">
         <v>1365</v>
@@ -12418,7 +12418,7 @@
         <v>111</v>
       </c>
       <c r="E137">
-        <v>0.23800000000000002</v>
+        <v>0.22312499999999999</v>
       </c>
       <c r="F137">
         <v>1365</v>
@@ -12474,7 +12474,7 @@
         <v>133</v>
       </c>
       <c r="E138">
-        <v>0.20299999999999996</v>
+        <v>0.19031249999999997</v>
       </c>
       <c r="F138">
         <v>1365</v>
@@ -12530,7 +12530,7 @@
         <v>88</v>
       </c>
       <c r="E139">
-        <v>0.25549999999999995</v>
+        <v>0.23953125</v>
       </c>
       <c r="F139">
         <v>1365</v>
@@ -12586,7 +12586,7 @@
         <v>93</v>
       </c>
       <c r="E140">
-        <v>0.25549999999999995</v>
+        <v>0.23953125</v>
       </c>
       <c r="F140">
         <v>1365</v>
@@ -12642,7 +12642,7 @@
         <v>243</v>
       </c>
       <c r="E141">
-        <v>0.25549999999999995</v>
+        <v>0.23953125</v>
       </c>
       <c r="F141">
         <v>1365</v>
@@ -12698,7 +12698,7 @@
         <v>245</v>
       </c>
       <c r="E142">
-        <v>0.25549999999999995</v>
+        <v>0.23953125</v>
       </c>
       <c r="F142">
         <v>1365</v>
@@ -12754,7 +12754,7 @@
         <v>247</v>
       </c>
       <c r="E143">
-        <v>0.25549999999999995</v>
+        <v>0.23953125</v>
       </c>
       <c r="F143">
         <v>1365</v>
@@ -12810,7 +12810,7 @@
         <v>247</v>
       </c>
       <c r="E144">
-        <v>0.25549999999999995</v>
+        <v>0.23953125</v>
       </c>
       <c r="F144">
         <v>1365</v>
@@ -12866,7 +12866,7 @@
         <v>245</v>
       </c>
       <c r="E145">
-        <v>0.25549999999999995</v>
+        <v>0.23953125</v>
       </c>
       <c r="F145">
         <v>1365</v>
@@ -12922,7 +12922,7 @@
         <v>243</v>
       </c>
       <c r="E146">
-        <v>0.24149999999999999</v>
+        <v>0.22640625</v>
       </c>
       <c r="F146">
         <v>1365</v>
@@ -12978,7 +12978,7 @@
         <v>88</v>
       </c>
       <c r="E147">
-        <v>0.24149999999999999</v>
+        <v>0.22640625</v>
       </c>
       <c r="F147">
         <v>1365</v>
@@ -13034,7 +13034,7 @@
         <v>216</v>
       </c>
       <c r="E148">
-        <v>0.23666129032258065</v>
+        <v>0.22186995967741935</v>
       </c>
       <c r="F148">
         <v>1365</v>
@@ -13090,7 +13090,7 @@
         <v>61</v>
       </c>
       <c r="E149">
-        <v>0.23450000000000004</v>
+        <v>0.21984375000000003</v>
       </c>
       <c r="F149">
         <v>1365</v>
@@ -13146,7 +13146,7 @@
         <v>255</v>
       </c>
       <c r="E150">
-        <v>0.24149999999999999</v>
+        <v>0.22640625</v>
       </c>
       <c r="F150">
         <v>1365</v>
@@ -13426,7 +13426,7 @@
         <v>582</v>
       </c>
       <c r="E155">
-        <v>0.17850000000000002</v>
+        <v>0.16734375000000001</v>
       </c>
       <c r="F155">
         <v>1365</v>
@@ -13482,7 +13482,7 @@
         <v>582</v>
       </c>
       <c r="E156">
-        <v>0.17850000000000002</v>
+        <v>0.16734375000000001</v>
       </c>
       <c r="F156">
         <v>1365</v>
@@ -13538,7 +13538,7 @@
         <v>582</v>
       </c>
       <c r="E157">
-        <v>0.17850000000000002</v>
+        <v>0.16734375000000001</v>
       </c>
       <c r="F157">
         <v>1365</v>
@@ -13594,7 +13594,7 @@
         <v>582</v>
       </c>
       <c r="E158">
-        <v>0.17850000000000002</v>
+        <v>0.16734375000000001</v>
       </c>
       <c r="F158">
         <v>1365</v>
@@ -13650,7 +13650,7 @@
         <v>582</v>
       </c>
       <c r="E159">
-        <v>0.17850000000000002</v>
+        <v>0.16734375000000001</v>
       </c>
       <c r="F159">
         <v>1365</v>
@@ -13706,7 +13706,7 @@
         <v>101</v>
       </c>
       <c r="E160">
-        <v>0.18900000000000003</v>
+        <v>0.1771875</v>
       </c>
       <c r="F160">
         <v>1365</v>
@@ -13762,7 +13762,7 @@
         <v>21</v>
       </c>
       <c r="E161">
-        <v>0.22750000000000001</v>
+        <v>0.21328125000000003</v>
       </c>
       <c r="F161">
         <v>1365</v>
@@ -13818,7 +13818,7 @@
         <v>21</v>
       </c>
       <c r="E162">
-        <v>0.20299999999999996</v>
+        <v>0.19031249999999997</v>
       </c>
       <c r="F162">
         <v>1365</v>
@@ -13874,7 +13874,7 @@
         <v>21</v>
       </c>
       <c r="E163">
-        <v>0.20299999999999996</v>
+        <v>0.19031249999999997</v>
       </c>
       <c r="F163">
         <v>1365</v>
@@ -13930,7 +13930,7 @@
         <v>21</v>
       </c>
       <c r="E164">
-        <v>0.20299999999999996</v>
+        <v>0.19031249999999997</v>
       </c>
       <c r="F164">
         <v>1365</v>
@@ -13986,7 +13986,7 @@
         <v>593</v>
       </c>
       <c r="E165">
-        <v>0.22400000000000003</v>
+        <v>0.21</v>
       </c>
       <c r="F165">
         <v>1365</v>
@@ -14042,7 +14042,7 @@
         <v>593</v>
       </c>
       <c r="E166">
-        <v>0.22400000000000003</v>
+        <v>0.21</v>
       </c>
       <c r="F166">
         <v>1365</v>
@@ -14098,7 +14098,7 @@
         <v>593</v>
       </c>
       <c r="E167">
-        <v>0.22400000000000003</v>
+        <v>0.21</v>
       </c>
       <c r="F167">
         <v>1365</v>
@@ -14149,7 +14149,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5375050F-B8DA-45AF-8497-C9A2E4D3B8BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB6CAB70-E745-469E-9C95-2DB487104E42}">
   <dimension ref="B9:T149"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21386,7 +21386,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3D1A311-68C5-433C-A77F-3F5BF9F13361}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC48455E-0482-4C56-8AA0-F97FBECF4EA2}">
   <dimension ref="B9:T679"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21471,7 +21471,7 @@
         <v>0.18923300970873791</v>
       </c>
       <c r="G11">
-        <v>0.26400000000000001</v>
+        <v>0.2475</v>
       </c>
       <c r="H11">
         <v>4024.9999999999995</v>
@@ -21524,7 +21524,7 @@
         <v>8.2000000000000003E-2</v>
       </c>
       <c r="G12">
-        <v>0.20400000000000001</v>
+        <v>0.19125</v>
       </c>
       <c r="H12">
         <v>4725</v>
@@ -21577,7 +21577,7 @@
         <v>0.10064077669902916</v>
       </c>
       <c r="G13">
-        <v>0.26400000000000001</v>
+        <v>0.2475</v>
       </c>
       <c r="H13">
         <v>4024.9999999999991</v>
@@ -21630,7 +21630,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
       <c r="G14">
-        <v>0.248</v>
+        <v>0.23249999999999998</v>
       </c>
       <c r="H14">
         <v>4024.9999999999991</v>
@@ -21683,7 +21683,7 @@
         <v>0.06</v>
       </c>
       <c r="G15">
-        <v>0.24799999999999997</v>
+        <v>0.23249999999999998</v>
       </c>
       <c r="H15">
         <v>4024.9999999999995</v>
@@ -21736,7 +21736,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="G16">
-        <v>0.21200000000000002</v>
+        <v>0.19875000000000001</v>
       </c>
       <c r="H16">
         <v>4024.9999999999991</v>
@@ -21789,7 +21789,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="G17">
-        <v>0.21200000000000002</v>
+        <v>0.19875000000000001</v>
       </c>
       <c r="H17">
         <v>4024.9999999999995</v>
@@ -21842,7 +21842,7 @@
         <v>6.3E-2</v>
       </c>
       <c r="G18">
-        <v>0.248</v>
+        <v>0.23249999999999998</v>
       </c>
       <c r="H18">
         <v>4024.9999999999995</v>
@@ -21895,7 +21895,7 @@
         <v>0.05</v>
       </c>
       <c r="G19">
-        <v>0.24</v>
+        <v>0.22499999999999998</v>
       </c>
       <c r="H19">
         <v>4725</v>
@@ -21948,7 +21948,7 @@
         <v>6.3E-2</v>
       </c>
       <c r="G20">
-        <v>0.248</v>
+        <v>0.23249999999999998</v>
       </c>
       <c r="H20">
         <v>4024.9999999999995</v>
@@ -22001,7 +22001,7 @@
         <v>0.06</v>
       </c>
       <c r="G21">
-        <v>0.24799999999999997</v>
+        <v>0.23249999999999998</v>
       </c>
       <c r="H21">
         <v>4024.9999999999995</v>
@@ -22054,7 +22054,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="G22">
-        <v>0.248</v>
+        <v>0.23250000000000001</v>
       </c>
       <c r="H22">
         <v>4024.9999999999995</v>
@@ -22107,7 +22107,7 @@
         <v>0.05</v>
       </c>
       <c r="G23">
-        <v>0.24</v>
+        <v>0.22499999999999998</v>
       </c>
       <c r="H23">
         <v>4725</v>
@@ -22160,7 +22160,7 @@
         <v>6.2E-2</v>
       </c>
       <c r="G24">
-        <v>0.248</v>
+        <v>0.23249999999999998</v>
       </c>
       <c r="H24">
         <v>4024.9999999999995</v>
@@ -22213,7 +22213,7 @@
         <v>0.20499999999999999</v>
       </c>
       <c r="G25">
-        <v>0.20400000000000001</v>
+        <v>0.19124999999999998</v>
       </c>
       <c r="H25">
         <v>4024.9999999999995</v>
@@ -22266,7 +22266,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="G26">
-        <v>0.22400000000000003</v>
+        <v>0.21000000000000002</v>
       </c>
       <c r="H26">
         <v>4725</v>
@@ -22319,7 +22319,7 @@
         <v>2.2679611650485442E-2</v>
       </c>
       <c r="G27">
-        <v>0.25600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H27">
         <v>4725</v>
@@ -22372,7 +22372,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="G28">
-        <v>0.192</v>
+        <v>0.18</v>
       </c>
       <c r="H28">
         <v>4725</v>
@@ -22425,7 +22425,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="G29">
-        <v>0.24</v>
+        <v>0.22499999999999998</v>
       </c>
       <c r="H29">
         <v>4725</v>
@@ -22478,7 +22478,7 @@
         <v>9.0718446601941768E-2</v>
       </c>
       <c r="G30">
-        <v>0.26400000000000001</v>
+        <v>0.2475</v>
       </c>
       <c r="H30">
         <v>4024.9999999999995</v>
@@ -22531,7 +22531,7 @@
         <v>0.04</v>
       </c>
       <c r="G31">
-        <v>0.24</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="H31">
         <v>4725</v>
@@ -22584,7 +22584,7 @@
         <v>8.2213592233009725E-2</v>
       </c>
       <c r="G32">
-        <v>0.26400000000000001</v>
+        <v>0.24749999999999997</v>
       </c>
       <c r="H32">
         <v>4024.9999999999995</v>
@@ -22637,7 +22637,7 @@
         <v>3.6145631067961176E-2</v>
       </c>
       <c r="G33">
-        <v>0.25600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H33">
         <v>4725</v>
@@ -22690,7 +22690,7 @@
         <v>6.2E-2</v>
       </c>
       <c r="G34">
-        <v>0.24</v>
+        <v>0.22499999999999998</v>
       </c>
       <c r="H34">
         <v>4725</v>
@@ -22743,7 +22743,7 @@
         <v>0.12402912621359226</v>
       </c>
       <c r="G35">
-        <v>0.26399999999999996</v>
+        <v>0.2475</v>
       </c>
       <c r="H35">
         <v>4024.9999999999995</v>
@@ -22796,7 +22796,7 @@
         <v>4.677669902912622E-2</v>
       </c>
       <c r="G36">
-        <v>0.25600000000000001</v>
+        <v>0.23999999999999996</v>
       </c>
       <c r="H36">
         <v>4725</v>
@@ -22849,7 +22849,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="G37">
-        <v>0.24000000000000002</v>
+        <v>0.22499999999999998</v>
       </c>
       <c r="H37">
         <v>4725</v>
@@ -22902,7 +22902,7 @@
         <v>3.0475728155339811E-2</v>
       </c>
       <c r="G38">
-        <v>0.25600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H38">
         <v>4725</v>
@@ -22955,7 +22955,7 @@
         <v>3.5436893203883497E-2</v>
       </c>
       <c r="G39">
-        <v>0.25600000000000001</v>
+        <v>0.24000000000000002</v>
       </c>
       <c r="H39">
         <v>4725</v>
@@ -23008,7 +23008,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="G40">
-        <v>0.24</v>
+        <v>0.22499999999999998</v>
       </c>
       <c r="H40">
         <v>4725</v>
@@ -23061,7 +23061,7 @@
         <v>2.6932038834951461E-2</v>
       </c>
       <c r="G41">
-        <v>0.25600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H41">
         <v>4725</v>
@@ -23114,7 +23114,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="G42">
-        <v>0.20400000000000001</v>
+        <v>0.19125</v>
       </c>
       <c r="H42">
         <v>4725</v>
@@ -23167,7 +23167,7 @@
         <v>2.4805825242718453E-2</v>
       </c>
       <c r="G43">
-        <v>0.25600000000000001</v>
+        <v>0.24000000000000002</v>
       </c>
       <c r="H43">
         <v>4725</v>
@@ -23220,7 +23220,7 @@
         <v>4.2524271844660198E-2</v>
       </c>
       <c r="G44">
-        <v>0.25600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H44">
         <v>4725</v>
@@ -23273,7 +23273,7 @@
         <v>0.03</v>
       </c>
       <c r="G45">
-        <v>0.20400000000000001</v>
+        <v>0.19125</v>
       </c>
       <c r="H45">
         <v>4725</v>
@@ -23326,7 +23326,7 @@
         <v>2.1262135922330099E-2</v>
       </c>
       <c r="G46">
-        <v>0.25600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H46">
         <v>4725</v>
@@ -23379,7 +23379,7 @@
         <v>0.03</v>
       </c>
       <c r="G47">
-        <v>0.23999999999999996</v>
+        <v>0.22499999999999998</v>
       </c>
       <c r="H47">
         <v>4725</v>
@@ -23432,7 +23432,7 @@
         <v>2.1262135922330099E-2</v>
       </c>
       <c r="G48">
-        <v>0.25600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H48">
         <v>4725</v>
@@ -23485,7 +23485,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="G49">
-        <v>0.22400000000000003</v>
+        <v>0.21000000000000002</v>
       </c>
       <c r="H49">
         <v>4725</v>
@@ -23538,7 +23538,7 @@
         <v>2.2679611650485442E-2</v>
       </c>
       <c r="G50">
-        <v>0.25600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H50">
         <v>4725</v>
@@ -23591,7 +23591,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="G51">
-        <v>0.22400000000000003</v>
+        <v>0.21000000000000002</v>
       </c>
       <c r="H51">
         <v>4725</v>
@@ -23644,7 +23644,7 @@
         <v>2.4805825242718453E-2</v>
       </c>
       <c r="G52">
-        <v>0.25600000000000001</v>
+        <v>0.24000000000000002</v>
       </c>
       <c r="H52">
         <v>4725</v>
@@ -23697,7 +23697,7 @@
         <v>3.9E-2</v>
       </c>
       <c r="G53">
-        <v>0.24</v>
+        <v>0.22499999999999995</v>
       </c>
       <c r="H53">
         <v>4725</v>
@@ -23750,7 +23750,7 @@
         <v>2.7640776699029129E-2</v>
       </c>
       <c r="G54">
-        <v>0.25600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H54">
         <v>4725</v>
@@ -23803,7 +23803,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G55">
-        <v>0.22400000000000006</v>
+        <v>0.21000000000000005</v>
       </c>
       <c r="H55">
         <v>4725</v>
@@ -23856,7 +23856,7 @@
         <v>7.0873786407766995E-2</v>
       </c>
       <c r="G56">
-        <v>0.26400000000000001</v>
+        <v>0.24749999999999997</v>
       </c>
       <c r="H56">
         <v>4025</v>
@@ -23909,7 +23909,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="G57">
-        <v>0.24000000000000002</v>
+        <v>0.22499999999999998</v>
       </c>
       <c r="H57">
         <v>4725</v>
@@ -23962,7 +23962,7 @@
         <v>2.5514563106796121E-2</v>
       </c>
       <c r="G58">
-        <v>0.25600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H58">
         <v>4725</v>
@@ -24015,7 +24015,7 @@
         <v>0.04</v>
       </c>
       <c r="G59">
-        <v>0.24</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="H59">
         <v>4725</v>
@@ -24068,7 +24068,7 @@
         <v>2.8349514563106804E-2</v>
       </c>
       <c r="G60">
-        <v>0.25600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H60">
         <v>4725</v>
@@ -24121,7 +24121,7 @@
         <v>0.16500000000000001</v>
       </c>
       <c r="G61">
-        <v>0.26400000000000001</v>
+        <v>0.2475</v>
       </c>
       <c r="H61">
         <v>2645</v>
@@ -24174,7 +24174,7 @@
         <v>0.11</v>
       </c>
       <c r="G62">
-        <v>0.22400000000000003</v>
+        <v>0.21000000000000002</v>
       </c>
       <c r="H62">
         <v>4140</v>
@@ -24227,7 +24227,7 @@
         <v>0.11</v>
       </c>
       <c r="G63">
-        <v>0.22400000000000003</v>
+        <v>0.21000000000000002</v>
       </c>
       <c r="H63">
         <v>4140</v>
@@ -24280,7 +24280,7 @@
         <v>0.433</v>
       </c>
       <c r="G64">
-        <v>0.27200000000000002</v>
+        <v>0.255</v>
       </c>
       <c r="H64">
         <v>2000</v>
@@ -24333,7 +24333,7 @@
         <v>0.49</v>
       </c>
       <c r="G65">
-        <v>0.28799999999999998</v>
+        <v>0.27</v>
       </c>
       <c r="H65">
         <v>2000</v>
@@ -24386,7 +24386,7 @@
         <v>0.29299999999999998</v>
       </c>
       <c r="G66">
-        <v>0.25600000000000001</v>
+        <v>0.23999999999999996</v>
       </c>
       <c r="H66">
         <v>2300</v>
@@ -24439,7 +24439,7 @@
         <v>0.43</v>
       </c>
       <c r="G67">
-        <v>0.27999999999999997</v>
+        <v>0.26249999999999996</v>
       </c>
       <c r="H67">
         <v>2000</v>
@@ -24492,7 +24492,7 @@
         <v>0.45</v>
       </c>
       <c r="G68">
-        <v>0.28799999999999998</v>
+        <v>0.27</v>
       </c>
       <c r="H68">
         <v>2000</v>
@@ -24545,7 +24545,7 @@
         <v>0.15</v>
       </c>
       <c r="G69">
-        <v>0.25600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H69">
         <v>2300</v>
@@ -24598,7 +24598,7 @@
         <v>0.15819999999999998</v>
       </c>
       <c r="G70">
-        <v>0.25600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H70">
         <v>2300</v>
@@ -24651,7 +24651,7 @@
         <v>0.15819999999999998</v>
       </c>
       <c r="G71">
-        <v>0.25600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H71">
         <v>2300</v>
@@ -24704,7 +24704,7 @@
         <v>0.15819999999999998</v>
       </c>
       <c r="G72">
-        <v>0.26400000000000001</v>
+        <v>0.2475</v>
       </c>
       <c r="H72">
         <v>2300</v>
@@ -24757,7 +24757,7 @@
         <v>0.15819999999999998</v>
       </c>
       <c r="G73">
-        <v>0.26400000000000001</v>
+        <v>0.2475</v>
       </c>
       <c r="H73">
         <v>2300</v>
@@ -24810,7 +24810,7 @@
         <v>0.152</v>
       </c>
       <c r="G74">
-        <v>0.24</v>
+        <v>0.22499999999999998</v>
       </c>
       <c r="H74">
         <v>2300</v>
@@ -24863,7 +24863,7 @@
         <v>0.158</v>
       </c>
       <c r="G75">
-        <v>0.27200000000000002</v>
+        <v>0.255</v>
       </c>
       <c r="H75">
         <v>2300</v>
@@ -24916,7 +24916,7 @@
         <v>0.15</v>
       </c>
       <c r="G76">
-        <v>0.25600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H76">
         <v>2300</v>
@@ -24969,7 +24969,7 @@
         <v>0.315</v>
       </c>
       <c r="G77">
-        <v>0.27200000000000002</v>
+        <v>0.255</v>
       </c>
       <c r="H77">
         <v>2000</v>
@@ -25022,7 +25022,7 @@
         <v>0.315</v>
       </c>
       <c r="G78">
-        <v>0.27999999999999997</v>
+        <v>0.26249999999999996</v>
       </c>
       <c r="H78">
         <v>2000</v>
@@ -25075,7 +25075,7 @@
         <v>0.3</v>
       </c>
       <c r="G79">
-        <v>0.27200000000000002</v>
+        <v>0.255</v>
       </c>
       <c r="H79">
         <v>2300</v>
@@ -25128,7 +25128,7 @@
         <v>0.46600000000000003</v>
       </c>
       <c r="G80">
-        <v>0.31600000000000006</v>
+        <v>0.29625000000000001</v>
       </c>
       <c r="H80">
         <v>2200</v>
@@ -25181,7 +25181,7 @@
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="G81">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="H81">
         <v>1150</v>
@@ -25234,7 +25234,7 @@
         <v>0.9</v>
       </c>
       <c r="G82">
-        <v>0.46399999999999997</v>
+        <v>0.43499999999999994</v>
       </c>
       <c r="H82">
         <v>1000</v>
@@ -25287,7 +25287,7 @@
         <v>0.45</v>
       </c>
       <c r="G83">
-        <v>0.48</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="H83">
         <v>1000</v>
@@ -25340,7 +25340,7 @@
         <v>0.45</v>
       </c>
       <c r="G84">
-        <v>0.48</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="H84">
         <v>1000</v>
@@ -25393,7 +25393,7 @@
         <v>0.35299999999999998</v>
       </c>
       <c r="G85">
-        <v>0.46400000000000002</v>
+        <v>0.43499999999999994</v>
       </c>
       <c r="H85">
         <v>1000</v>
@@ -25446,7 +25446,7 @@
         <v>0.36</v>
       </c>
       <c r="G86">
-        <v>0.47999999999999993</v>
+        <v>0.4499999999999999</v>
       </c>
       <c r="H86">
         <v>1000</v>
@@ -25499,7 +25499,7 @@
         <v>0.12</v>
       </c>
       <c r="G87">
-        <v>0.41600000000000004</v>
+        <v>0.39</v>
       </c>
       <c r="H87">
         <v>1150</v>
@@ -25552,7 +25552,7 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="G88">
-        <v>0.41600000000000004</v>
+        <v>0.39</v>
       </c>
       <c r="H88">
         <v>1150</v>
@@ -25605,7 +25605,7 @@
         <v>0.1</v>
       </c>
       <c r="G89">
-        <v>0.41600000000000004</v>
+        <v>0.39</v>
       </c>
       <c r="H89">
         <v>1150</v>
@@ -25658,7 +25658,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G90">
-        <v>0.43600000000000005</v>
+        <v>0.40875000000000006</v>
       </c>
       <c r="H90">
         <v>1000</v>
@@ -25711,7 +25711,7 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="G91">
-        <v>0.43600000000000005</v>
+        <v>0.40875000000000006</v>
       </c>
       <c r="H91">
         <v>1000</v>
@@ -25764,7 +25764,7 @@
         <v>0.32</v>
       </c>
       <c r="G92">
-        <v>0.43600000000000005</v>
+        <v>0.40875000000000006</v>
       </c>
       <c r="H92">
         <v>1000</v>
@@ -25817,7 +25817,7 @@
         <v>0.156</v>
       </c>
       <c r="G93">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="H93">
         <v>1150</v>
@@ -25870,7 +25870,7 @@
         <v>0.12</v>
       </c>
       <c r="G94">
-        <v>0.41600000000000004</v>
+        <v>0.39</v>
       </c>
       <c r="H94">
         <v>1150</v>
@@ -25923,7 +25923,7 @@
         <v>0.249</v>
       </c>
       <c r="G95">
-        <v>0.41600000000000004</v>
+        <v>0.39</v>
       </c>
       <c r="H95">
         <v>1150</v>
@@ -25976,7 +25976,7 @@
         <v>0.11799999999999999</v>
       </c>
       <c r="G96">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="H96">
         <v>1150</v>
@@ -26029,7 +26029,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="G97">
-        <v>0.48000000000000004</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="H97">
         <v>1000</v>
@@ -26082,7 +26082,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="G98">
-        <v>0.48000000000000004</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="H98">
         <v>1000</v>
@@ -26135,7 +26135,7 @@
         <v>0.875</v>
       </c>
       <c r="G99">
-        <v>0.43600000000000005</v>
+        <v>0.40875000000000006</v>
       </c>
       <c r="H99">
         <v>1000</v>
@@ -26188,7 +26188,7 @@
         <v>0.3</v>
       </c>
       <c r="G100">
-        <v>0.44800000000000001</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="H100">
         <v>1150</v>
@@ -26241,7 +26241,7 @@
         <v>1.038</v>
       </c>
       <c r="G101">
-        <v>0.43600000000000005</v>
+        <v>0.40875000000000006</v>
       </c>
       <c r="H101">
         <v>1000</v>
@@ -26294,7 +26294,7 @@
         <v>0.12</v>
       </c>
       <c r="G102">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="H102">
         <v>1150</v>
@@ -26347,7 +26347,7 @@
         <v>0.27500000000000002</v>
       </c>
       <c r="G103">
-        <v>0.41600000000000004</v>
+        <v>0.39</v>
       </c>
       <c r="H103">
         <v>1150</v>
@@ -26400,7 +26400,7 @@
         <v>0.11</v>
       </c>
       <c r="G104">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="H104">
         <v>1150</v>
@@ -26453,7 +26453,7 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="G105">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="H105">
         <v>1150</v>
@@ -26506,7 +26506,7 @@
         <v>0.48</v>
       </c>
       <c r="G106">
-        <v>0.43600000000000005</v>
+        <v>0.40875000000000006</v>
       </c>
       <c r="H106">
         <v>1000</v>
@@ -26559,7 +26559,7 @@
         <v>0.10100000000000001</v>
       </c>
       <c r="G107">
-        <v>0.41600000000000004</v>
+        <v>0.39</v>
       </c>
       <c r="H107">
         <v>1150</v>
@@ -26612,7 +26612,7 @@
         <v>0.10100000000000001</v>
       </c>
       <c r="G108">
-        <v>0.41600000000000004</v>
+        <v>0.39</v>
       </c>
       <c r="H108">
         <v>1150</v>
@@ -26665,7 +26665,7 @@
         <v>0.19500000000000001</v>
       </c>
       <c r="G109">
-        <v>0.41600000000000004</v>
+        <v>0.38999999999999996</v>
       </c>
       <c r="H109">
         <v>1150</v>
@@ -26718,7 +26718,7 @@
         <v>0.22800000000000001</v>
       </c>
       <c r="G110">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="H110">
         <v>1150</v>
@@ -26771,7 +26771,7 @@
         <v>0.68300000000000005</v>
       </c>
       <c r="G111">
-        <v>0.436</v>
+        <v>0.40875000000000006</v>
       </c>
       <c r="H111">
         <v>1000</v>
@@ -26824,7 +26824,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G112">
-        <v>0.43600000000000005</v>
+        <v>0.40875000000000006</v>
       </c>
       <c r="H112">
         <v>1000</v>
@@ -26877,7 +26877,7 @@
         <v>0.28599999999999998</v>
       </c>
       <c r="G113">
-        <v>0.44800000000000006</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="H113">
         <v>1150</v>
@@ -26930,7 +26930,7 @@
         <v>0.224</v>
       </c>
       <c r="G114">
-        <v>0.41600000000000004</v>
+        <v>0.39</v>
       </c>
       <c r="H114">
         <v>1150</v>
@@ -26983,7 +26983,7 @@
         <v>0.14099999999999999</v>
       </c>
       <c r="G115">
-        <v>0.27200000000000002</v>
+        <v>0.255</v>
       </c>
       <c r="H115">
         <v>1150</v>
@@ -27036,7 +27036,7 @@
         <v>0.499</v>
       </c>
       <c r="G116">
-        <v>0.43600000000000005</v>
+        <v>0.40875000000000006</v>
       </c>
       <c r="H116">
         <v>1000</v>
@@ -27089,7 +27089,7 @@
         <v>0.86</v>
       </c>
       <c r="G117">
-        <v>0.46399999999999997</v>
+        <v>0.43499999999999994</v>
       </c>
       <c r="H117">
         <v>1000</v>
@@ -27142,7 +27142,7 @@
         <v>0.29199999999999998</v>
       </c>
       <c r="G118">
-        <v>0.41600000000000004</v>
+        <v>0.39</v>
       </c>
       <c r="H118">
         <v>1150</v>
@@ -27195,7 +27195,7 @@
         <v>0.29199999999999998</v>
       </c>
       <c r="G119">
-        <v>0.41600000000000004</v>
+        <v>0.39</v>
       </c>
       <c r="H119">
         <v>1150</v>
@@ -27248,7 +27248,7 @@
         <v>0.40300000000000002</v>
       </c>
       <c r="G120">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="H120">
         <v>1000</v>
@@ -27301,7 +27301,7 @@
         <v>0.40300000000000002</v>
       </c>
       <c r="G121">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="H121">
         <v>1000</v>
@@ -27354,7 +27354,7 @@
         <v>0.26500000000000001</v>
       </c>
       <c r="G122">
-        <v>0.41600000000000004</v>
+        <v>0.39</v>
       </c>
       <c r="H122">
         <v>1150</v>
@@ -27407,7 +27407,7 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="G123">
-        <v>0.41600000000000004</v>
+        <v>0.39</v>
       </c>
       <c r="H123">
         <v>1150</v>
@@ -27460,7 +27460,7 @@
         <v>0.13539999999999999</v>
       </c>
       <c r="G124">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="H124">
         <v>1150</v>
@@ -27513,7 +27513,7 @@
         <v>0.11</v>
       </c>
       <c r="G125">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="H125">
         <v>1150</v>
@@ -27566,7 +27566,7 @@
         <v>9.8000000000000004E-2</v>
       </c>
       <c r="G126">
-        <v>0.41599999999999998</v>
+        <v>0.39</v>
       </c>
       <c r="H126">
         <v>1150</v>
@@ -27619,7 +27619,7 @@
         <v>0.1</v>
       </c>
       <c r="G127">
-        <v>0.44800000000000006</v>
+        <v>0.4200000000000001</v>
       </c>
       <c r="H127">
         <v>1150</v>
@@ -27672,7 +27672,7 @@
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="G128">
-        <v>0.46399999999999997</v>
+        <v>0.43499999999999989</v>
       </c>
       <c r="H128">
         <v>1150</v>
@@ -27725,7 +27725,7 @@
         <v>0.20399999999999999</v>
       </c>
       <c r="G129">
-        <v>0.44800000000000006</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="H129">
         <v>1150</v>
@@ -27778,7 +27778,7 @@
         <v>0.14099999999999999</v>
       </c>
       <c r="G130">
-        <v>0.27200000000000002</v>
+        <v>0.255</v>
       </c>
       <c r="H130">
         <v>1150</v>
@@ -27831,7 +27831,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="G131">
-        <v>0.41600000000000009</v>
+        <v>0.38999999999999996</v>
       </c>
       <c r="H131">
         <v>1150</v>
@@ -27884,7 +27884,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="G132">
-        <v>0.44800000000000006</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="H132">
         <v>1150</v>
@@ -27937,7 +27937,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
       <c r="G133">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="H133">
         <v>1150</v>
@@ -27990,7 +27990,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="G134">
-        <v>0.44800000000000012</v>
+        <v>0.42000000000000004</v>
       </c>
       <c r="H134">
         <v>1150</v>
@@ -28043,7 +28043,7 @@
         <v>0.08</v>
       </c>
       <c r="G135">
-        <v>0.21200000000000002</v>
+        <v>0.19875000000000001</v>
       </c>
       <c r="H135">
         <v>919.99999999999977</v>
@@ -28096,7 +28096,7 @@
         <v>0.10299999999999999</v>
       </c>
       <c r="G136">
-        <v>0.21200000000000002</v>
+        <v>0.19875000000000001</v>
       </c>
       <c r="H136">
         <v>919.99999999999989</v>
@@ -28149,7 +28149,7 @@
         <v>0.10299999999999999</v>
       </c>
       <c r="G137">
-        <v>0.21200000000000002</v>
+        <v>0.19875000000000001</v>
       </c>
       <c r="H137">
         <v>919.99999999999989</v>
@@ -28202,7 +28202,7 @@
         <v>0.10299999999999999</v>
       </c>
       <c r="G138">
-        <v>0.21200000000000002</v>
+        <v>0.19875000000000001</v>
       </c>
       <c r="H138">
         <v>919.99999999999989</v>
@@ -28255,7 +28255,7 @@
         <v>0.10299999999999999</v>
       </c>
       <c r="G139">
-        <v>0.21200000000000002</v>
+        <v>0.19875000000000001</v>
       </c>
       <c r="H139">
         <v>919.99999999999989</v>
@@ -28308,7 +28308,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G140">
-        <v>0.23199999999999998</v>
+        <v>0.21749999999999997</v>
       </c>
       <c r="H140">
         <v>919.99999999999989</v>
@@ -28361,7 +28361,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G141">
-        <v>0.23199999999999998</v>
+        <v>0.21749999999999997</v>
       </c>
       <c r="H141">
         <v>919.99999999999989</v>
@@ -28414,7 +28414,7 @@
         <v>0.1</v>
       </c>
       <c r="G142">
-        <v>0.23199999999999998</v>
+        <v>0.21749999999999997</v>
       </c>
       <c r="H142">
         <v>919.99999999999989</v>
@@ -28467,7 +28467,7 @@
         <v>0.1</v>
       </c>
       <c r="G143">
-        <v>0.23199999999999998</v>
+        <v>0.21749999999999997</v>
       </c>
       <c r="H143">
         <v>919.99999999999989</v>
@@ -28520,7 +28520,7 @@
         <v>0.105</v>
       </c>
       <c r="G144">
-        <v>0.248</v>
+        <v>0.23249999999999998</v>
       </c>
       <c r="H144">
         <v>919.99999999999989</v>
@@ -28573,7 +28573,7 @@
         <v>0.10299999999999999</v>
       </c>
       <c r="G145">
-        <v>0.23199999999999998</v>
+        <v>0.21749999999999997</v>
       </c>
       <c r="H145">
         <v>919.99999999999989</v>
@@ -28626,7 +28626,7 @@
         <v>0.20399999999999999</v>
       </c>
       <c r="G146">
-        <v>0.248</v>
+        <v>0.23250000000000001</v>
       </c>
       <c r="H146">
         <v>919.99999999999989</v>
@@ -28679,7 +28679,7 @@
         <v>0.16500000000000001</v>
       </c>
       <c r="G147">
-        <v>0.23199999999999996</v>
+        <v>0.21749999999999997</v>
       </c>
       <c r="H147">
         <v>919.99999999999977</v>
@@ -28732,7 +28732,7 @@
         <v>0.1</v>
       </c>
       <c r="G148">
-        <v>0.21200000000000002</v>
+        <v>0.19875000000000001</v>
       </c>
       <c r="H148">
         <v>919.99999999999989</v>
@@ -28785,7 +28785,7 @@
         <v>0.17</v>
       </c>
       <c r="G149">
-        <v>0.24799999999999997</v>
+        <v>0.23249999999999998</v>
       </c>
       <c r="H149">
         <v>919.99999999999977</v>
@@ -28838,7 +28838,7 @@
         <v>0.09</v>
       </c>
       <c r="G150">
-        <v>0.23199999999999998</v>
+        <v>0.21749999999999994</v>
       </c>
       <c r="H150">
         <v>919.99999999999989</v>
@@ -28891,7 +28891,7 @@
         <v>0.1</v>
       </c>
       <c r="G151">
-        <v>0.21200000000000002</v>
+        <v>0.19875000000000001</v>
       </c>
       <c r="H151">
         <v>919.99999999999989</v>
@@ -28944,7 +28944,7 @@
         <v>0.22800000000000001</v>
       </c>
       <c r="G152">
-        <v>0.248</v>
+        <v>0.23249999999999998</v>
       </c>
       <c r="H152">
         <v>919.99999999999989</v>
@@ -28997,7 +28997,7 @@
         <v>0.22800000000000001</v>
       </c>
       <c r="G153">
-        <v>0.248</v>
+        <v>0.23249999999999998</v>
       </c>
       <c r="H153">
         <v>919.99999999999989</v>
@@ -29050,7 +29050,7 @@
         <v>0.15</v>
       </c>
       <c r="G154">
-        <v>0.21200000000000002</v>
+        <v>0.19875000000000001</v>
       </c>
       <c r="H154">
         <v>919.99999999999977</v>
@@ -29103,7 +29103,7 @@
         <v>0.1</v>
       </c>
       <c r="G155">
-        <v>0.21200000000000002</v>
+        <v>0.19875000000000001</v>
       </c>
       <c r="H155">
         <v>919.99999999999989</v>
@@ -29156,7 +29156,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="G156">
-        <v>0.248</v>
+        <v>0.23249999999999996</v>
       </c>
       <c r="H156">
         <v>919.99999999999989</v>
@@ -29209,7 +29209,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
       <c r="G157">
-        <v>0.248</v>
+        <v>0.23249999999999998</v>
       </c>
       <c r="H157">
         <v>919.99999999999989</v>
@@ -29262,7 +29262,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G158">
-        <v>0.24800000000000003</v>
+        <v>0.23250000000000001</v>
       </c>
       <c r="H158">
         <v>919.99999999999977</v>
@@ -29315,7 +29315,7 @@
         <v>0.16</v>
       </c>
       <c r="G159">
-        <v>0.23199999999999998</v>
+        <v>0.21749999999999997</v>
       </c>
       <c r="H159">
         <v>919.99999999999977</v>
@@ -29368,7 +29368,7 @@
         <v>0.05</v>
       </c>
       <c r="G160">
-        <v>0.20400000000000001</v>
+        <v>0.19125</v>
       </c>
       <c r="H160">
         <v>1080</v>
@@ -29421,7 +29421,7 @@
         <v>0.10199999999999999</v>
       </c>
       <c r="G161">
-        <v>0.25600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H161">
         <v>919.99999999999989</v>
@@ -29474,7 +29474,7 @@
         <v>0.42499999999999999</v>
       </c>
       <c r="G162">
-        <v>0.23199999999999998</v>
+        <v>0.21749999999999997</v>
       </c>
       <c r="H162">
         <v>919.99999999999989</v>
@@ -29527,7 +29527,7 @@
         <v>0.05</v>
       </c>
       <c r="G163">
-        <v>0.22400000000000003</v>
+        <v>0.21000000000000005</v>
       </c>
       <c r="H163">
         <v>1080</v>
@@ -29580,7 +29580,7 @@
         <v>0.05</v>
       </c>
       <c r="G164">
-        <v>0.22400000000000003</v>
+        <v>0.21000000000000005</v>
       </c>
       <c r="H164">
         <v>1080</v>
@@ -29633,7 +29633,7 @@
         <v>0.17</v>
       </c>
       <c r="G165">
-        <v>0.23199999999999998</v>
+        <v>0.21749999999999997</v>
       </c>
       <c r="H165">
         <v>919.99999999999977</v>
@@ -29686,7 +29686,7 @@
         <v>7.8E-2</v>
       </c>
       <c r="G166">
-        <v>0.21200000000000002</v>
+        <v>0.19875000000000001</v>
       </c>
       <c r="H166">
         <v>919.99999999999977</v>
@@ -29739,7 +29739,7 @@
         <v>5.5E-2</v>
       </c>
       <c r="G167">
-        <v>0.23199999999999998</v>
+        <v>0.21749999999999997</v>
       </c>
       <c r="H167">
         <v>919.99999999999989</v>
@@ -29792,7 +29792,7 @@
         <v>0.12</v>
       </c>
       <c r="G168">
-        <v>0.21200000000000002</v>
+        <v>0.19875000000000001</v>
       </c>
       <c r="H168">
         <v>919.99999999999989</v>
@@ -29845,7 +29845,7 @@
         <v>0.15</v>
       </c>
       <c r="G169">
-        <v>0.24800000000000003</v>
+        <v>0.23250000000000001</v>
       </c>
       <c r="H169">
         <v>1380</v>
@@ -29898,7 +29898,7 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="G170">
-        <v>0.26400000000000001</v>
+        <v>0.2475</v>
       </c>
       <c r="H170">
         <v>1200</v>
@@ -29951,7 +29951,7 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="G171">
-        <v>0.26400000000000001</v>
+        <v>0.2475</v>
       </c>
       <c r="H171">
         <v>1200</v>
@@ -30004,7 +30004,7 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="G172">
-        <v>0.26400000000000001</v>
+        <v>0.2475</v>
       </c>
       <c r="H172">
         <v>1200</v>
@@ -30057,7 +30057,7 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="G173">
-        <v>0.26400000000000001</v>
+        <v>0.2475</v>
       </c>
       <c r="H173">
         <v>1200</v>
@@ -30110,7 +30110,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="G174">
-        <v>0.27200000000000002</v>
+        <v>0.255</v>
       </c>
       <c r="H174">
         <v>1380</v>
@@ -30163,7 +30163,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="G175">
-        <v>0.23199999999999998</v>
+        <v>0.21749999999999997</v>
       </c>
       <c r="H175">
         <v>1380</v>
@@ -30216,7 +30216,7 @@
         <v>0.42199999999999999</v>
       </c>
       <c r="G176">
-        <v>0.29199999999999998</v>
+        <v>0.27374999999999999</v>
       </c>
       <c r="H176">
         <v>1200</v>
@@ -30269,7 +30269,7 @@
         <v>0.46600000000000003</v>
       </c>
       <c r="G177">
-        <v>0.29199999999999998</v>
+        <v>0.27374999999999999</v>
       </c>
       <c r="H177">
         <v>1200</v>
@@ -30322,7 +30322,7 @@
         <v>0.38500000000000001</v>
       </c>
       <c r="G178">
-        <v>0.29199999999999998</v>
+        <v>0.27374999999999999</v>
       </c>
       <c r="H178">
         <v>1200</v>
@@ -30375,7 +30375,7 @@
         <v>0.46300000000000002</v>
       </c>
       <c r="G179">
-        <v>0.29199999999999998</v>
+        <v>0.27374999999999999</v>
       </c>
       <c r="H179">
         <v>1200</v>
@@ -30428,7 +30428,7 @@
         <v>0.39</v>
       </c>
       <c r="G180">
-        <v>0.29199999999999998</v>
+        <v>0.27374999999999999</v>
       </c>
       <c r="H180">
         <v>1200</v>
@@ -30481,7 +30481,7 @@
         <v>0.39</v>
       </c>
       <c r="G181">
-        <v>0.29199999999999998</v>
+        <v>0.27374999999999999</v>
       </c>
       <c r="H181">
         <v>1200</v>
@@ -30534,7 +30534,7 @@
         <v>0.4032</v>
       </c>
       <c r="G182">
-        <v>0.29199999999999998</v>
+        <v>0.27374999999999999</v>
       </c>
       <c r="H182">
         <v>1200</v>
@@ -30587,7 +30587,7 @@
         <v>0.155</v>
       </c>
       <c r="G183">
-        <v>0.27599999999999997</v>
+        <v>0.25874999999999998</v>
       </c>
       <c r="H183">
         <v>1380</v>
@@ -30640,7 +30640,7 @@
         <v>0.113</v>
       </c>
       <c r="G184">
-        <v>0.27599999999999997</v>
+        <v>0.25874999999999998</v>
       </c>
       <c r="H184">
         <v>1380</v>
@@ -30693,7 +30693,7 @@
         <v>0.217</v>
       </c>
       <c r="G185">
-        <v>0.27047004608294933</v>
+        <v>0.25356566820276499</v>
       </c>
       <c r="H185">
         <v>1545.8986175115208</v>
@@ -30746,7 +30746,7 @@
         <v>0.05</v>
       </c>
       <c r="G186">
-        <v>0.26800000000000002</v>
+        <v>0.25125000000000003</v>
       </c>
       <c r="H186">
         <v>1620</v>
@@ -30799,7 +30799,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="G187">
-        <v>0.27599999999999997</v>
+        <v>0.25874999999999998</v>
       </c>
       <c r="H187">
         <v>1380</v>
@@ -44568,7 +44568,7 @@
         <v>0.1</v>
       </c>
       <c r="G458">
-        <v>0.20400000000000001</v>
+        <v>0.19125</v>
       </c>
       <c r="H458">
         <v>1035</v>
@@ -44621,7 +44621,7 @@
         <v>0.1</v>
       </c>
       <c r="G459">
-        <v>0.20400000000000001</v>
+        <v>0.19125</v>
       </c>
       <c r="H459">
         <v>1035</v>
@@ -44674,7 +44674,7 @@
         <v>0.1</v>
       </c>
       <c r="G460">
-        <v>0.20400000000000001</v>
+        <v>0.19125</v>
       </c>
       <c r="H460">
         <v>1035</v>
@@ -44727,7 +44727,7 @@
         <v>0.1</v>
       </c>
       <c r="G461">
-        <v>0.20400000000000001</v>
+        <v>0.19125</v>
       </c>
       <c r="H461">
         <v>1035</v>
@@ -44780,7 +44780,7 @@
         <v>0.1</v>
       </c>
       <c r="G462">
-        <v>0.20400000000000001</v>
+        <v>0.19125</v>
       </c>
       <c r="H462">
         <v>1035</v>
@@ -44833,7 +44833,7 @@
         <v>0.05</v>
       </c>
       <c r="G463">
-        <v>0.21600000000000003</v>
+        <v>0.20250000000000001</v>
       </c>
       <c r="H463">
         <v>1215</v>
@@ -44886,7 +44886,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="G464">
-        <v>0.24399999999999999</v>
+        <v>0.22875000000000001</v>
       </c>
       <c r="H464">
         <v>1150</v>
@@ -44939,7 +44939,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="G465">
-        <v>0.26</v>
+        <v>0.24375000000000002</v>
       </c>
       <c r="H465">
         <v>1150</v>
@@ -44992,7 +44992,7 @@
         <v>0.1633</v>
       </c>
       <c r="G466">
-        <v>0.23199999999999996</v>
+        <v>0.21749999999999997</v>
       </c>
       <c r="H466">
         <v>1494.9999999999998</v>
@@ -45045,7 +45045,7 @@
         <v>0.1633</v>
       </c>
       <c r="G467">
-        <v>0.23199999999999996</v>
+        <v>0.21749999999999997</v>
       </c>
       <c r="H467">
         <v>1494.9999999999998</v>
@@ -45098,7 +45098,7 @@
         <v>0.1633</v>
       </c>
       <c r="G468">
-        <v>0.23199999999999996</v>
+        <v>0.21749999999999997</v>
       </c>
       <c r="H468">
         <v>1494.9999999999998</v>
@@ -45151,7 +45151,7 @@
         <v>0.35</v>
       </c>
       <c r="G469">
-        <v>0.25600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H469">
         <v>1300</v>
@@ -45204,7 +45204,7 @@
         <v>0.35</v>
       </c>
       <c r="G470">
-        <v>0.25600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H470">
         <v>1300</v>
@@ -45257,7 +45257,7 @@
         <v>0.35</v>
       </c>
       <c r="G471">
-        <v>0.25600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H471">
         <v>1300</v>
@@ -45316,7 +45316,7 @@
         <v>33</v>
       </c>
       <c r="L472">
-        <v>0.20066638501093176</v>
+        <v>0.20066638501093173</v>
       </c>
       <c r="N472" t="s">
         <v>726</v>
@@ -45325,7 +45325,7 @@
         <v>652</v>
       </c>
       <c r="P472" t="s">
-        <v>857</v>
+        <v>732</v>
       </c>
       <c r="Q472" t="s">
         <v>728</v>
@@ -45363,7 +45363,7 @@
         <v>33</v>
       </c>
       <c r="L473">
-        <v>0.20066638501093176</v>
+        <v>0.20066638501093173</v>
       </c>
       <c r="N473" t="s">
         <v>726</v>
@@ -45372,7 +45372,7 @@
         <v>652</v>
       </c>
       <c r="P473" t="s">
-        <v>732</v>
+        <v>857</v>
       </c>
       <c r="Q473" t="s">
         <v>728</v>
@@ -45410,7 +45410,7 @@
         <v>33</v>
       </c>
       <c r="L474">
-        <v>0.20066638501093176</v>
+        <v>0.20066638501093173</v>
       </c>
       <c r="N474" t="s">
         <v>726</v>
@@ -46147,7 +46147,7 @@
         <v>677</v>
       </c>
       <c r="P487" t="s">
-        <v>857</v>
+        <v>732</v>
       </c>
       <c r="Q487" t="s">
         <v>728</v>
@@ -46203,7 +46203,7 @@
         <v>677</v>
       </c>
       <c r="P488" t="s">
-        <v>732</v>
+        <v>857</v>
       </c>
       <c r="Q488" t="s">
         <v>728</v>
@@ -52893,7 +52893,7 @@
         <v>47</v>
       </c>
       <c r="L662">
-        <v>0.35543377524859943</v>
+        <v>0.35543377524859937</v>
       </c>
     </row>
     <row r="663" spans="2:12" x14ac:dyDescent="0.45">
@@ -52928,7 +52928,7 @@
         <v>45</v>
       </c>
       <c r="L663">
-        <v>0.35543377524859943</v>
+        <v>0.35543377524859937</v>
       </c>
     </row>
     <row r="664" spans="2:12" x14ac:dyDescent="0.45">
@@ -53497,7 +53497,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9F4F3AD-70B6-40C2-82B7-746BC03FE446}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C753CAC-C625-4B90-B256-69FEE0725480}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_CAN_grids_kan/vt_vervestacks_CAN_v1.xlsx
+++ b/VerveStacks_CAN_grids_kan/vt_vervestacks_CAN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CAFB607C-C0A2-4C9D-AE3E-BDC82AC83B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D6E642C-0A64-4A80-8753-7F3E15FD3180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{35E67FDF-80B3-47C0-9A0F-275E0FEB12DC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6024F2D7-C5A5-46B1-80BD-138C79C238FD}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -5060,7 +5060,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C9BC0F5-C438-4876-8973-F9E7C43636D7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3BC3B00-E3B7-4A82-A760-4308CB51697A}">
   <dimension ref="B9:O14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5283,7 +5283,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1A523E-2E2E-4C21-A83D-E3F4A87FDF5E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4917E801-7A96-4863-858F-ACE292B95179}">
   <dimension ref="B9:T167"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14149,7 +14149,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB6CAB70-E745-469E-9C95-2DB487104E42}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D068B375-6A50-499D-82DD-1C7F8EA1D5D3}">
   <dimension ref="B9:T149"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21386,7 +21386,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC48455E-0482-4C56-8AA0-F97FBECF4EA2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{222C46C8-8DDE-4ADD-922E-BF53913343F0}">
   <dimension ref="B9:T679"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -53497,7 +53497,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C753CAC-C625-4B90-B256-69FEE0725480}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C8C2D0-5AE3-4A7B-A385-FE51E6C219EA}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
